--- a/server/templates/SMP-Visualisation-Residential-MixedUse.xlsx
+++ b/server/templates/SMP-Visualisation-Residential-MixedUse.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amina_0soxtza\Dropbox\GIW TEAM\GIW\8_Templates\Calculator Templates\SMP Visualisation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inesb\Desktop\Claude Code\server\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F373706D-1D3C-45E1-A5FE-BB9A25BE36A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5C0CE2-A6E2-4CAB-8C29-A498664E13CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="780" xr2:uid="{ABC4B530-0DF2-4B7A-AC79-6C340B5D949E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="780" activeTab="1" xr2:uid="{ABC4B530-0DF2-4B7A-AC79-6C340B5D949E}"/>
   </bookViews>
   <sheets>
     <sheet name="Final Report" sheetId="12" r:id="rId1"/>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="281">
   <si>
     <t>Development</t>
   </si>
@@ -1033,9 +1033,6 @@
   </si>
   <si>
     <t>1505 Point Nepean</t>
-  </si>
-  <si>
-    <t>Address</t>
   </si>
   <si>
     <t>*All results are indicative only, based on preliminary assumptions.</t>
@@ -1487,7 +1484,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1714,13 +1711,7 @@
     <xf numFmtId="9" fontId="14" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1732,7 +1723,19 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1744,17 +1747,6 @@
     <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1955,22 +1947,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)">
-                  <c:v>5036.2903229835483</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13235.370967741936</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)">
-                  <c:v>14889.792338709674</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)">
-                  <c:v>42971.906249999993</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)">
-                  <c:v>3161.8125</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)">
-                  <c:v>8590</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1990,7 +1982,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> Address </c:v>
+                  <c:v> -   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2055,22 +2047,22 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>5613.0267954542451</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13235.370967741936</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11911.833870967743</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13424.423512500001</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13687.412400000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6013</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2390,7 +2382,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>With Green Power</c:v>
@@ -2405,13 +2397,13 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>75.581248246314232</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>54.941158090130976</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54.941158090130976</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2457,7 +2449,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>With Green Power</c:v>
@@ -2472,13 +2464,13 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>21.531251499928317</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21.531251499928317</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>21.531251499928317</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2524,7 +2516,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>With Green Power</c:v>
@@ -2539,13 +2531,13 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2591,7 +2583,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>With Green Power</c:v>
@@ -2606,13 +2598,13 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2658,7 +2650,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>With Green Power</c:v>
@@ -2673,13 +2665,13 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>6.387104966399999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.387104966399999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.387104966399999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2728,7 +2720,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>With Green Power</c:v>
@@ -2746,10 +2738,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-10.492000000000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-10.492000000000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3167,7 +3159,7 @@
                 <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1885.8052829127489</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3316,7 +3308,7 @@
                 <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1693.2543211771172</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3336,7 +3328,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> Address </c:v>
+                  <c:v> -   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3399,7 +3391,7 @@
                       <a:pPr/>
                       <a:t>[VALUE]</a:t>
                     </a:fld>
-                    <a:endParaRPr lang="en-AU"/>
+                    <a:endParaRPr lang="en-CA"/>
                   </a:p>
                 </c:rich>
               </c:tx>
@@ -3490,7 +3482,7 @@
                 <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1230.8523013990584</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3819,25 +3811,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)">
-                  <c:v>5036.2903229835483</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13235.370967741936</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)">
-                  <c:v>14889.792338709674</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)">
-                  <c:v>42971.906249999993</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)">
-                  <c:v>3161.8125</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)">
-                  <c:v>8590</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)">
-                  <c:v>87885.172379435156</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3857,7 +3849,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> Address </c:v>
+                  <c:v> -   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3908,25 +3900,25 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>5613.0267954542451</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13235.370967741936</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11911.833870967743</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13424.423512500001</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13687.412400000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6013</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>63885.067546663922</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4302,7 +4294,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4314,10 +4306,10 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>87885.172379435156</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>63885.067546663922</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4415,7 +4407,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4427,10 +4419,10 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>24344.080888888886</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24344.080888888886</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4528,7 +4520,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4540,10 +4532,10 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4587,7 +4579,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4599,10 +4591,10 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4701,7 +4693,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4713,10 +4705,10 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>7426.8662399999994</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7426.8662399999994</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4760,7 +4752,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4775,7 +4767,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-12200</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5154,7 +5146,7 @@
                   <c:v> Min. BCA 2022 Compliance </c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v> Address </c:v>
+                  <c:v> -   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5166,10 +5158,10 @@
                 <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>97.032526889483023</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>108.14431625908512</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5265,7 +5257,7 @@
                   <c:v> Min. BCA 2022 Compliance </c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v> Address </c:v>
+                  <c:v> -   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5277,10 +5269,10 @@
                 <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>255.00148064516128</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>255.00148064516128</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5376,7 +5368,7 @@
                   <c:v> Min. BCA 2022 Compliance </c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v> Address </c:v>
+                  <c:v> -   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5388,10 +5380,10 @@
                 <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>286.87666572580639</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>229.50133258064517</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5487,7 +5479,7 @@
                   <c:v> Min. BCA 2022 Compliance </c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v> Address </c:v>
+                  <c:v> -   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5499,10 +5491,10 @@
                 <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>827.92539374999978</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>258.64389300750003</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5598,7 +5590,7 @@
                   <c:v> Min. BCA 2022 Compliance </c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v> Address </c:v>
+                  <c:v> -   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5610,10 +5602,10 @@
                 <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>60.917587499999996</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>263.71081224</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5709,7 +5701,7 @@
                   <c:v> Min. BCA 2022 Compliance </c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v> Address </c:v>
+                  <c:v> -   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5721,10 +5713,10 @@
                 <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>165.50066666666666</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>115.85046666666666</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6128,7 +6120,7 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -6143,10 +6135,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>17519.887872000003</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6166,7 +6158,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> Address </c:v>
+                  <c:v> -   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6217,7 +6209,7 @@
                 <c:formatCode>_-* #,##0.0000000_-;\-* #,##0.0000000_-;_-* "-"???????_-;_-@_-</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -6232,10 +6224,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6557,7 +6549,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>With Green Power</c:v>
@@ -6572,13 +6564,13 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>75.581248246314232</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>54.941158090130976</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54.941158090130976</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6676,7 +6668,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>With Green Power</c:v>
@@ -6691,13 +6683,13 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>21.531251499928317</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21.531251499928317</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>21.531251499928317</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6741,7 +6733,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>With Green Power</c:v>
@@ -6756,13 +6748,13 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6806,7 +6798,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>With Green Power</c:v>
@@ -6821,13 +6813,13 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6969,7 +6961,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>With Green Power</c:v>
@@ -6984,13 +6976,13 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>6.387104966399999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.387104966399999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.387104966399999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7034,7 +7026,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>With Green Power</c:v>
@@ -7052,10 +7044,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-10.492000000000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-10.492000000000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7450,7 +7442,7 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -7485,7 +7477,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7533,7 +7525,7 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -13820,8 +13812,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1181099" y="6858000"/>
-              <a:ext cx="5419725" cy="2897505"/>
+              <a:off x="1203959" y="6515100"/>
+              <a:ext cx="5604510" cy="2754630"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -13840,7 +13832,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100"/>
+                <a:rPr lang="en-CA" sz="1100"/>
                 <a:t>This chart isn't available in your version of Excel.
 Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
               </a:r>
@@ -14639,35 +14631,35 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="B1:V27"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="5.7109375" style="23" customWidth="1"/>
-    <col min="3" max="3" width="2.42578125" style="23" customWidth="1"/>
-    <col min="4" max="5" width="5.7109375" style="23" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" style="23" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" style="23" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" style="23" customWidth="1"/>
-    <col min="9" max="9" width="4.85546875" style="23" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" style="23" customWidth="1"/>
-    <col min="11" max="11" width="3.140625" style="23" customWidth="1"/>
-    <col min="12" max="12" width="5.28515625" style="23" customWidth="1"/>
-    <col min="13" max="13" width="5.5703125" style="23" customWidth="1"/>
-    <col min="14" max="15" width="5.7109375" style="23" customWidth="1"/>
-    <col min="16" max="16" width="5.140625" style="23" customWidth="1"/>
-    <col min="17" max="17" width="5.85546875" style="23" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" style="23" customWidth="1"/>
-    <col min="19" max="19" width="6.42578125" style="23" customWidth="1"/>
-    <col min="20" max="20" width="6.140625" style="23" customWidth="1"/>
-    <col min="21" max="21" width="3.140625" style="23" customWidth="1"/>
-    <col min="22" max="37" width="5.7109375" style="23" customWidth="1"/>
-    <col min="38" max="16384" width="8.85546875" style="23"/>
+    <col min="1" max="2" width="5.6640625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="2.44140625" style="23" customWidth="1"/>
+    <col min="4" max="5" width="5.6640625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="4.5546875" style="23" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" style="23" customWidth="1"/>
+    <col min="8" max="8" width="4.33203125" style="23" customWidth="1"/>
+    <col min="9" max="9" width="4.88671875" style="23" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" style="23" customWidth="1"/>
+    <col min="11" max="11" width="3.109375" style="23" customWidth="1"/>
+    <col min="12" max="12" width="5.33203125" style="23" customWidth="1"/>
+    <col min="13" max="13" width="5.5546875" style="23" customWidth="1"/>
+    <col min="14" max="15" width="5.6640625" style="23" customWidth="1"/>
+    <col min="16" max="16" width="5.109375" style="23" customWidth="1"/>
+    <col min="17" max="17" width="5.88671875" style="23" customWidth="1"/>
+    <col min="18" max="18" width="5.5546875" style="23" customWidth="1"/>
+    <col min="19" max="19" width="6.44140625" style="23" customWidth="1"/>
+    <col min="20" max="20" width="6.109375" style="23" customWidth="1"/>
+    <col min="21" max="21" width="3.109375" style="23" customWidth="1"/>
+    <col min="22" max="37" width="5.6640625" style="23" customWidth="1"/>
+    <col min="38" max="16384" width="8.88671875" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:22" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="116"/>
       <c r="V1" s="116"/>
     </row>
-    <row r="2" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C2" s="27"/>
       <c r="D2" s="27"/>
       <c r="E2" s="27"/>
@@ -14688,7 +14680,7 @@
       <c r="T2" s="27"/>
       <c r="U2" s="27"/>
     </row>
-    <row r="3" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="27"/>
       <c r="D3" s="27"/>
       <c r="E3" s="27"/>
@@ -14709,7 +14701,7 @@
       <c r="T3" s="27"/>
       <c r="U3" s="27"/>
     </row>
-    <row r="4" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="27"/>
       <c r="D4" s="27"/>
       <c r="E4" s="27"/>
@@ -14730,7 +14722,7 @@
       <c r="T4" s="27"/>
       <c r="U4" s="27"/>
     </row>
-    <row r="5" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="27"/>
       <c r="D5" s="27"/>
       <c r="E5" s="27"/>
@@ -14751,7 +14743,7 @@
       <c r="T5" s="27"/>
       <c r="U5" s="27"/>
     </row>
-    <row r="6" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="27"/>
       <c r="D6" s="27"/>
       <c r="E6" s="27"/>
@@ -14772,7 +14764,7 @@
       <c r="T6" s="27"/>
       <c r="U6" s="27"/>
     </row>
-    <row r="7" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
       <c r="E7" s="27"/>
@@ -14793,7 +14785,7 @@
       <c r="T7" s="27"/>
       <c r="U7" s="27"/>
     </row>
-    <row r="8" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="27"/>
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
@@ -14814,11 +14806,11 @@
       <c r="T8" s="27"/>
       <c r="U8" s="27"/>
     </row>
-    <row r="9" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="27"/>
-      <c r="D9" s="125">
+      <c r="D9" s="125" t="e">
         <f>'Totals Residential &amp; Mixed-Use'!F16</f>
-        <v>24000.104832771234</v>
+        <v>#N/A</v>
       </c>
       <c r="E9" s="126"/>
       <c r="F9" s="126"/>
@@ -14842,7 +14834,7 @@
       <c r="T9" s="124"/>
       <c r="U9" s="27"/>
     </row>
-    <row r="10" spans="2:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="27"/>
       <c r="D10" s="27"/>
       <c r="E10" s="27"/>
@@ -14863,7 +14855,7 @@
       <c r="T10" s="27"/>
       <c r="U10" s="27"/>
     </row>
-    <row r="11" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="27"/>
       <c r="D11" s="27"/>
       <c r="E11" s="110"/>
@@ -14884,7 +14876,7 @@
       <c r="T11" s="27"/>
       <c r="U11" s="27"/>
     </row>
-    <row r="12" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
       <c r="E12" s="27"/>
@@ -14905,7 +14897,7 @@
       <c r="T12" s="27"/>
       <c r="U12" s="27"/>
     </row>
-    <row r="13" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="27"/>
       <c r="D13" s="27"/>
       <c r="E13" s="27"/>
@@ -14926,7 +14918,7 @@
       <c r="T13" s="27"/>
       <c r="U13" s="27"/>
     </row>
-    <row r="14" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="27"/>
       <c r="D14" s="27"/>
       <c r="E14" s="27"/>
@@ -14947,7 +14939,7 @@
       <c r="T14" s="27"/>
       <c r="U14" s="27"/>
     </row>
-    <row r="15" spans="2:22" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:22" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="27"/>
       <c r="D15" s="27"/>
       <c r="E15" s="27"/>
@@ -14968,7 +14960,7 @@
       <c r="T15" s="27"/>
       <c r="U15" s="27"/>
     </row>
-    <row r="16" spans="2:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="27"/>
       <c r="D16" s="27"/>
       <c r="E16" s="27"/>
@@ -14989,11 +14981,11 @@
       <c r="T16" s="27"/>
       <c r="U16" s="27"/>
     </row>
-    <row r="17" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="27"/>
-      <c r="D17" s="129">
+      <c r="D17" s="129" t="e">
         <f>'Totals Residential &amp; Mixed-Use'!K63</f>
-        <v>0.30079429039964678</v>
+        <v>#N/A</v>
       </c>
       <c r="E17" s="129"/>
       <c r="F17" s="108" t="s">
@@ -15017,7 +15009,7 @@
       <c r="T17" s="124"/>
       <c r="U17" s="27"/>
     </row>
-    <row r="18" spans="2:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="27"/>
       <c r="D18" s="27"/>
       <c r="E18" s="27"/>
@@ -15038,7 +15030,7 @@
       <c r="T18" s="27"/>
       <c r="U18" s="27"/>
     </row>
-    <row r="19" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="27"/>
       <c r="D19" s="27"/>
       <c r="E19" s="27"/>
@@ -15059,7 +15051,7 @@
       <c r="T19" s="27"/>
       <c r="U19" s="27"/>
     </row>
-    <row r="20" spans="2:22" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:22" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C20" s="27"/>
       <c r="D20" s="27"/>
       <c r="E20" s="27"/>
@@ -15080,7 +15072,7 @@
       <c r="T20" s="27"/>
       <c r="U20" s="27"/>
     </row>
-    <row r="21" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C21" s="27"/>
       <c r="D21" s="27"/>
       <c r="E21" s="27"/>
@@ -15101,11 +15093,11 @@
       <c r="T21" s="27"/>
       <c r="U21" s="27"/>
     </row>
-    <row r="22" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C22" s="27"/>
-      <c r="D22" s="123">
+      <c r="D22" s="123" t="e">
         <f>'Totals Residential &amp; Mixed-Use'!Y17</f>
-        <v>462.40201977805873</v>
+        <v>#N/A</v>
       </c>
       <c r="E22" s="123"/>
       <c r="F22" s="123"/>
@@ -15127,7 +15119,7 @@
       <c r="T22" s="114"/>
       <c r="U22" s="27"/>
     </row>
-    <row r="23" spans="2:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C23" s="27"/>
       <c r="D23" s="96"/>
       <c r="E23" s="96"/>
@@ -15148,11 +15140,11 @@
       <c r="T23" s="114"/>
       <c r="U23" s="27"/>
     </row>
-    <row r="24" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C24" s="27"/>
-      <c r="D24" s="123">
+      <c r="D24" s="123" t="e">
         <f>'Totals Residential &amp; Mixed-Use'!X17</f>
-        <v>654.95298151369047</v>
+        <v>#N/A</v>
       </c>
       <c r="E24" s="123"/>
       <c r="F24" s="123"/>
@@ -15174,12 +15166,11 @@
       <c r="T24" s="114"/>
       <c r="U24" s="115"/>
     </row>
-    <row r="25" spans="2:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="144"/>
+    <row r="25" spans="2:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D25" s="96"/>
-      <c r="E25" s="142"/>
+      <c r="E25" s="27"/>
       <c r="F25" s="96"/>
-      <c r="G25" s="143"/>
+      <c r="G25" s="114"/>
       <c r="H25" s="114"/>
       <c r="I25" s="114"/>
       <c r="J25" s="114"/>
@@ -15193,20 +15184,15 @@
       <c r="R25" s="114"/>
       <c r="S25" s="114"/>
       <c r="T25" s="107" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="U25" s="114"/>
     </row>
-    <row r="26" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="116"/>
-      <c r="C26" s="144"/>
-      <c r="D26" s="144"/>
-      <c r="E26" s="144"/>
-      <c r="F26" s="144"/>
-      <c r="G26" s="144"/>
       <c r="V26" s="116"/>
     </row>
-    <row r="27" spans="2:22" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:22" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C27" s="94"/>
       <c r="D27" s="95"/>
       <c r="E27" s="95"/>
@@ -15245,23 +15231,23 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC07E4BE-C962-4C7E-AA01-A850DDE55B29}">
   <dimension ref="B2:M24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19.7109375" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" customWidth="1"/>
-    <col min="11" max="12" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.6640625" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" customWidth="1"/>
+    <col min="11" max="12" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="J2" s="141" t="s">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="J2" s="138" t="s">
         <v>62</v>
       </c>
-      <c r="K2" s="141"/>
-      <c r="L2" s="141"/>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
       <c r="J3">
         <v>3</v>
       </c>
@@ -15275,7 +15261,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>27</v>
       </c>
@@ -15298,7 +15284,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>28</v>
       </c>
@@ -15321,7 +15307,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>29</v>
       </c>
@@ -15344,7 +15330,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>34</v>
       </c>
@@ -15367,7 +15353,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>35</v>
       </c>
@@ -15375,7 +15361,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="I9" t="s">
         <v>58</v>
       </c>
@@ -15389,7 +15375,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
       <c r="I10">
         <v>6</v>
       </c>
@@ -15404,7 +15390,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>38</v>
       </c>
@@ -15415,7 +15401,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>39</v>
       </c>
@@ -15423,7 +15409,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>40</v>
       </c>
@@ -15431,7 +15417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>41</v>
       </c>
@@ -15442,12 +15428,12 @@
         <v>212</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
       <c r="I15" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>42</v>
       </c>
@@ -15464,7 +15450,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>43</v>
       </c>
@@ -15478,7 +15464,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>44</v>
       </c>
@@ -15493,7 +15479,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>45</v>
       </c>
@@ -15508,7 +15494,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>229</v>
       </c>
@@ -15522,7 +15508,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>131</v>
       </c>
@@ -15530,7 +15516,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
         <v>28</v>
       </c>
@@ -15538,7 +15524,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
         <v>29</v>
       </c>
@@ -15566,22 +15552,22 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC94C4A-4031-4B7A-B54E-5F499B381D6C}">
   <dimension ref="B3:Q40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -15625,7 +15611,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>141</v>
       </c>
@@ -15675,7 +15661,7 @@
         <v>30.298115896211506</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>148</v>
       </c>
@@ -15725,7 +15711,7 @@
         <v>5.7022058823529411</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>161</v>
       </c>
@@ -15775,7 +15761,7 @@
         <v>12.261522346368714</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>253</v>
       </c>
@@ -15825,7 +15811,7 @@
         <v>11.306772908366533</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>254</v>
       </c>
@@ -15875,7 +15861,7 @@
         <v>11.441176470588236</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>255</v>
       </c>
@@ -15925,7 +15911,7 @@
         <v>8.3451327433628322</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F10" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -15963,7 +15949,7 @@
         <v>8.6241457858769923</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F11" s="16" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -16004,7 +15990,7 @@
         <v>6.3094839142091157</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="G12" t="s">
         <v>267</v>
       </c>
@@ -16040,10 +16026,10 @@
         <v>9.2532810635759333</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="Q13" s="16"/>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>2</v>
       </c>
@@ -16066,7 +16052,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>149</v>
       </c>
@@ -16099,7 +16085,7 @@
         <v>11.504648556768091</v>
       </c>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>150</v>
       </c>
@@ -16125,7 +16111,7 @@
         <v>52.291581108829568</v>
       </c>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>151</v>
       </c>
@@ -16172,7 +16158,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>152</v>
       </c>
@@ -16222,7 +16208,7 @@
         <v>36.023529411764706</v>
       </c>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>153</v>
       </c>
@@ -16272,7 +16258,7 @@
         <v>32.159430835152399</v>
       </c>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>154</v>
       </c>
@@ -16322,7 +16308,7 @@
         <v>44.576761240682856</v>
       </c>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>155</v>
       </c>
@@ -16372,7 +16358,7 @@
         <v>21.396190739206482</v>
       </c>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>156</v>
       </c>
@@ -16398,7 +16384,7 @@
         <v>9.4357682619647356</v>
       </c>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>157</v>
       </c>
@@ -16431,7 +16417,7 @@
         <v>33.538978056701609</v>
       </c>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>158</v>
       </c>
@@ -16457,7 +16443,7 @@
         <v>8.6748329621380851</v>
       </c>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>159</v>
       </c>
@@ -16483,7 +16469,7 @@
         <v>14.919491083533215</v>
       </c>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>160</v>
       </c>
@@ -16509,7 +16495,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="G28" t="s">
         <v>267</v>
       </c>
@@ -16518,7 +16504,7 @@
         <v>16.707620165569967</v>
       </c>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>256</v>
       </c>
@@ -16541,7 +16527,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>273</v>
       </c>
@@ -16567,7 +16553,7 @@
         <v>22.614721243775051</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>274</v>
       </c>
@@ -16593,7 +16579,7 @@
         <v>26.217015423911974</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>275</v>
       </c>
@@ -16619,7 +16605,7 @@
         <v>30.92134576040009</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>276</v>
       </c>
@@ -16645,7 +16631,7 @@
         <v>136.85220820189275</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>277</v>
       </c>
@@ -16671,7 +16657,7 @@
         <v>29.419473361910597</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>278</v>
       </c>
@@ -16697,7 +16683,7 @@
         <v>32.409725654967872</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="F38" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
@@ -16711,7 +16697,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="G40" t="s">
         <v>267</v>
       </c>
@@ -16728,51 +16714,51 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49BA68A7-AA1D-4556-81AD-C23148F90A2E}">
   <dimension ref="A1:U70"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" style="27" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" style="23" customWidth="1"/>
-    <col min="3" max="3" width="35.7109375" style="23" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" style="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="23"/>
-    <col min="7" max="7" width="3.42578125" style="23" customWidth="1"/>
-    <col min="8" max="8" width="35.7109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.44140625" style="27" customWidth="1"/>
+    <col min="2" max="2" width="4.6640625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="35.6640625" style="23" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="23"/>
+    <col min="7" max="7" width="3.44140625" style="23" customWidth="1"/>
+    <col min="8" max="8" width="35.6640625" style="23" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" style="23"/>
-    <col min="12" max="12" width="35.7109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" style="23" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.85546875" style="23"/>
-    <col min="16" max="16" width="34.140625" style="27" customWidth="1"/>
-    <col min="17" max="21" width="8.85546875" style="27"/>
-    <col min="22" max="16384" width="8.85546875" style="23"/>
+    <col min="10" max="10" width="10.6640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" style="23"/>
+    <col min="12" max="12" width="35.6640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5546875" style="23" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.88671875" style="23"/>
+    <col min="16" max="16" width="34.109375" style="27" customWidth="1"/>
+    <col min="17" max="21" width="8.88671875" style="27"/>
+    <col min="22" max="16384" width="8.88671875" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" s="27" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:15" s="27" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:15" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B3" s="130" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="131"/>
-      <c r="D3" s="131"/>
-      <c r="E3" s="132"/>
+    <row r="1" spans="2:15" s="27" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:15" s="27" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:15" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="B3" s="134" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="136"/>
       <c r="F3" s="27"/>
-      <c r="G3" s="133" t="s">
+      <c r="G3" s="131" t="s">
         <v>51</v>
       </c>
-      <c r="H3" s="134"/>
-      <c r="I3" s="134"/>
-      <c r="J3" s="135"/>
+      <c r="H3" s="132"/>
+      <c r="I3" s="132"/>
+      <c r="J3" s="133"/>
       <c r="K3" s="27"/>
       <c r="L3" s="27"/>
       <c r="M3" s="27"/>
       <c r="N3" s="27"/>
       <c r="O3" s="27"/>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B4" s="26"/>
       <c r="C4" s="27"/>
       <c r="D4" s="27"/>
@@ -16788,14 +16774,12 @@
       <c r="N4" s="27"/>
       <c r="O4" s="27"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" s="26"/>
       <c r="C5" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="D5" s="68" t="s">
-        <v>279</v>
-      </c>
+      <c r="D5" s="68"/>
       <c r="E5" s="28"/>
       <c r="F5" s="27"/>
       <c r="G5" s="26"/>
@@ -16808,23 +16792,19 @@
       <c r="N5" s="27"/>
       <c r="O5" s="27"/>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="26"/>
       <c r="C6" s="35" t="s">
         <v>251</v>
       </c>
-      <c r="D6" s="65">
-        <v>15</v>
-      </c>
+      <c r="D6" s="65"/>
       <c r="E6" s="28"/>
       <c r="F6" s="27"/>
       <c r="G6" s="26"/>
       <c r="H6" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="66" t="s">
-        <v>55</v>
-      </c>
+      <c r="I6" s="66"/>
       <c r="J6" s="28"/>
       <c r="K6" s="27"/>
       <c r="L6" s="27"/>
@@ -16832,15 +16812,12 @@
       <c r="N6" s="27"/>
       <c r="O6" s="27"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="26"/>
       <c r="C7" s="35" t="s">
         <v>252</v>
       </c>
-      <c r="D7" s="92">
-        <f>3747/62</f>
-        <v>60.435483870967744</v>
-      </c>
+      <c r="D7" s="92"/>
       <c r="E7" s="28" t="s">
         <v>7</v>
       </c>
@@ -16849,9 +16826,7 @@
       <c r="H7" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="66">
-        <v>6</v>
-      </c>
+      <c r="I7" s="66"/>
       <c r="J7" s="28"/>
       <c r="K7" s="27"/>
       <c r="L7" s="27"/>
@@ -16859,7 +16834,7 @@
       <c r="N7" s="27"/>
       <c r="O7" s="27"/>
     </row>
-    <row r="8" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="26"/>
       <c r="C8" s="35" t="s">
         <v>1</v>
@@ -16879,14 +16854,12 @@
       <c r="N8" s="27"/>
       <c r="O8" s="27"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="26"/>
       <c r="C9" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="65">
-        <v>0</v>
-      </c>
+      <c r="D9" s="65"/>
       <c r="E9" s="28" t="s">
         <v>7</v>
       </c>
@@ -16901,15 +16874,12 @@
       <c r="N9" s="27"/>
       <c r="O9" s="27"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="26"/>
       <c r="C10" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="65">
-        <f>45.3+56.28+5.72</f>
-        <v>107.3</v>
-      </c>
+      <c r="D10" s="65"/>
       <c r="E10" s="28" t="s">
         <v>7</v>
       </c>
@@ -16924,15 +16894,12 @@
       <c r="N10" s="27"/>
       <c r="O10" s="27"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="26"/>
       <c r="C11" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="65">
-        <f>(43*13)-56.28</f>
-        <v>502.72</v>
-      </c>
+      <c r="D11" s="65"/>
       <c r="E11" s="28" t="s">
         <v>7</v>
       </c>
@@ -16947,15 +16914,12 @@
       <c r="N11" s="27"/>
       <c r="O11" s="27"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="26"/>
       <c r="C12" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="65">
-        <f>276.3+29.7+19.44</f>
-        <v>325.44</v>
-      </c>
+      <c r="D12" s="65"/>
       <c r="E12" s="28" t="s">
         <v>7</v>
       </c>
@@ -16970,7 +16934,7 @@
       <c r="N12" s="27"/>
       <c r="O12" s="27"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" s="26"/>
       <c r="C13" s="35" t="s">
         <v>6</v>
@@ -16990,14 +16954,12 @@
       <c r="N13" s="27"/>
       <c r="O13" s="27"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" s="26"/>
       <c r="C14" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="D14" s="65">
-        <v>2</v>
-      </c>
+      <c r="D14" s="65"/>
       <c r="E14" s="28"/>
       <c r="F14" s="27"/>
       <c r="G14" s="27"/>
@@ -17010,14 +16972,12 @@
       <c r="N14" s="27"/>
       <c r="O14" s="27"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B15" s="26"/>
       <c r="C15" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="D15" s="65">
-        <v>46.51</v>
-      </c>
+      <c r="D15" s="65"/>
       <c r="E15" s="28" t="s">
         <v>164</v>
       </c>
@@ -17032,7 +16992,7 @@
       <c r="N15" s="27"/>
       <c r="O15" s="27"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B16" s="26"/>
       <c r="C16" s="27"/>
       <c r="D16" s="27"/>
@@ -17048,7 +17008,7 @@
       <c r="N16" s="27"/>
       <c r="O16" s="27"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="26"/>
       <c r="C17" s="35" t="s">
         <v>212</v>
@@ -17066,7 +17026,7 @@
       <c r="N17" s="27"/>
       <c r="O17" s="27"/>
     </row>
-    <row r="18" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="29"/>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
@@ -17082,26 +17042,26 @@
       <c r="N18" s="27"/>
       <c r="O18" s="27"/>
     </row>
-    <row r="19" spans="2:15" s="27" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="2:15" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B20" s="130" t="s">
+    <row r="19" spans="2:15" s="27" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="2:15" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="B20" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="131"/>
-      <c r="D20" s="131"/>
-      <c r="E20" s="131"/>
-      <c r="F20" s="131"/>
-      <c r="G20" s="131"/>
-      <c r="H20" s="131"/>
-      <c r="I20" s="131"/>
-      <c r="J20" s="131"/>
-      <c r="K20" s="131"/>
-      <c r="L20" s="131"/>
-      <c r="M20" s="131"/>
-      <c r="N20" s="131"/>
-      <c r="O20" s="132"/>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C20" s="135"/>
+      <c r="D20" s="135"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="135"/>
+      <c r="H20" s="135"/>
+      <c r="I20" s="135"/>
+      <c r="J20" s="135"/>
+      <c r="K20" s="135"/>
+      <c r="L20" s="135"/>
+      <c r="M20" s="135"/>
+      <c r="N20" s="135"/>
+      <c r="O20" s="136"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="26"/>
       <c r="C21" s="31"/>
       <c r="D21" s="27"/>
@@ -17117,35 +17077,33 @@
       <c r="N21" s="27"/>
       <c r="O21" s="28"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B22" s="26"/>
-      <c r="C22" s="136" t="s">
+      <c r="C22" s="130" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="136"/>
-      <c r="E22" s="136"/>
+      <c r="D22" s="130"/>
+      <c r="E22" s="130"/>
       <c r="F22" s="27"/>
       <c r="G22" s="27"/>
-      <c r="H22" s="136" t="s">
+      <c r="H22" s="130" t="s">
         <v>1</v>
       </c>
-      <c r="I22" s="136"/>
-      <c r="J22" s="136"/>
-      <c r="L22" s="136" t="s">
+      <c r="I22" s="130"/>
+      <c r="J22" s="130"/>
+      <c r="L22" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="M22" s="136"/>
-      <c r="N22" s="136"/>
+      <c r="M22" s="130"/>
+      <c r="N22" s="130"/>
       <c r="O22" s="28"/>
     </row>
-    <row r="23" spans="2:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B23" s="26"/>
       <c r="C23" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="68">
-        <v>7.5</v>
-      </c>
+      <c r="D23" s="68"/>
       <c r="E23" s="36" t="s">
         <v>8</v>
       </c>
@@ -17170,14 +17128,12 @@
       </c>
       <c r="O23" s="28"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="26"/>
       <c r="C24" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="68">
-        <v>51.2</v>
-      </c>
+      <c r="D24" s="68"/>
       <c r="E24" s="35" t="s">
         <v>49</v>
       </c>
@@ -17200,14 +17156,12 @@
       <c r="N24" s="36"/>
       <c r="O24" s="28"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" s="26"/>
       <c r="C25" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="68">
-        <v>17.899999999999999</v>
-      </c>
+      <c r="D25" s="68"/>
       <c r="E25" s="36" t="s">
         <v>49</v>
       </c>
@@ -17236,7 +17190,7 @@
       </c>
       <c r="O25" s="28"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="26"/>
       <c r="C26" s="33" t="s">
         <v>32</v>
@@ -17268,7 +17222,7 @@
       </c>
       <c r="O26" s="28"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" s="26"/>
       <c r="C27" s="33" t="s">
         <v>33</v>
@@ -17282,9 +17236,7 @@
       <c r="H27" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="I27" s="66" t="s">
-        <v>229</v>
-      </c>
+      <c r="I27" s="66"/>
       <c r="J27" s="35"/>
       <c r="K27" s="27"/>
       <c r="L27" s="27"/>
@@ -17292,7 +17244,7 @@
       <c r="N27" s="27"/>
       <c r="O27" s="28"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" s="26"/>
       <c r="C28" s="33" t="s">
         <v>36</v>
@@ -17317,7 +17269,7 @@
       <c r="N28" s="27"/>
       <c r="O28" s="28"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="26"/>
       <c r="C29" s="33" t="s">
         <v>37</v>
@@ -17342,7 +17294,7 @@
       <c r="N29" s="27"/>
       <c r="O29" s="28"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B30" s="26"/>
       <c r="C30" s="33" t="s">
         <v>19</v>
@@ -17359,14 +17311,14 @@
       <c r="I30" s="27"/>
       <c r="J30" s="27"/>
       <c r="K30" s="27"/>
-      <c r="L30" s="136" t="s">
+      <c r="L30" s="130" t="s">
         <v>176</v>
       </c>
-      <c r="M30" s="136"/>
-      <c r="N30" s="136"/>
+      <c r="M30" s="130"/>
+      <c r="N30" s="130"/>
       <c r="O30" s="28"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="26"/>
       <c r="C31" s="33" t="s">
         <v>21</v>
@@ -17379,11 +17331,11 @@
       </c>
       <c r="F31" s="27"/>
       <c r="G31" s="27"/>
-      <c r="H31" s="136" t="s">
+      <c r="H31" s="130" t="s">
         <v>176</v>
       </c>
-      <c r="I31" s="136"/>
-      <c r="J31" s="136"/>
+      <c r="I31" s="130"/>
+      <c r="J31" s="130"/>
       <c r="K31" s="27"/>
       <c r="L31" s="36" t="s">
         <v>192</v>
@@ -17394,13 +17346,13 @@
       </c>
       <c r="O31" s="28"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="26"/>
       <c r="C32" s="33" t="s">
         <v>42</v>
       </c>
       <c r="D32" s="66" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E32" s="35"/>
       <c r="F32" s="27"/>
@@ -17422,14 +17374,12 @@
       </c>
       <c r="O32" s="28"/>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B33" s="26"/>
       <c r="C33" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="D33" s="66">
-        <v>8590</v>
-      </c>
+      <c r="D33" s="66"/>
       <c r="E33" s="35" t="s">
         <v>22</v>
       </c>
@@ -17452,14 +17402,12 @@
       </c>
       <c r="O33" s="28"/>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B34" s="26"/>
       <c r="C34" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="66">
-        <v>6013</v>
-      </c>
+      <c r="D34" s="66"/>
       <c r="E34" s="35" t="s">
         <v>22</v>
       </c>
@@ -17482,7 +17430,7 @@
       </c>
       <c r="O34" s="28"/>
     </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B35" s="26"/>
       <c r="C35" s="27"/>
       <c r="D35" s="27"/>
@@ -17506,7 +17454,7 @@
       </c>
       <c r="O35" s="28"/>
     </row>
-    <row r="36" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B36" s="26"/>
       <c r="C36" s="56"/>
       <c r="D36" s="67"/>
@@ -17530,7 +17478,7 @@
       </c>
       <c r="O36" s="28"/>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B37" s="26"/>
       <c r="C37" s="56"/>
       <c r="D37" s="67"/>
@@ -17549,7 +17497,7 @@
       <c r="N37" s="36"/>
       <c r="O37" s="28"/>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B38" s="26"/>
       <c r="C38" s="27"/>
       <c r="D38" s="27"/>
@@ -17568,7 +17516,7 @@
       </c>
       <c r="O38" s="28"/>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B39" s="26"/>
       <c r="C39" s="27"/>
       <c r="D39" s="27"/>
@@ -17592,14 +17540,12 @@
       </c>
       <c r="O39" s="28"/>
     </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B40" s="26"/>
       <c r="C40" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="D40" s="66">
-        <v>12200</v>
-      </c>
+      <c r="D40" s="66"/>
       <c r="E40" s="27" t="s">
         <v>22</v>
       </c>
@@ -17622,7 +17568,7 @@
       </c>
       <c r="O40" s="28"/>
     </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B41" s="26"/>
       <c r="C41" s="35" t="s">
         <v>248</v>
@@ -17650,7 +17596,7 @@
       </c>
       <c r="O41" s="28"/>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B42" s="26"/>
       <c r="C42" s="27"/>
       <c r="D42" s="27"/>
@@ -17674,7 +17620,7 @@
       </c>
       <c r="O42" s="28"/>
     </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B43" s="26"/>
       <c r="C43" s="27"/>
       <c r="D43" s="27"/>
@@ -17698,7 +17644,7 @@
       </c>
       <c r="O43" s="28"/>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B44" s="26"/>
       <c r="C44" s="27"/>
       <c r="D44" s="27"/>
@@ -17718,7 +17664,7 @@
       <c r="N44" s="27"/>
       <c r="O44" s="28"/>
     </row>
-    <row r="45" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="29"/>
       <c r="C45" s="25"/>
       <c r="D45" s="25"/>
@@ -17734,7 +17680,7 @@
       <c r="N45" s="25"/>
       <c r="O45" s="30"/>
     </row>
-    <row r="46" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B46" s="27"/>
       <c r="C46" s="27"/>
       <c r="D46" s="27"/>
@@ -17750,29 +17696,29 @@
       <c r="N46" s="27"/>
       <c r="O46" s="27"/>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B47" s="133" t="s">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B47" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="134"/>
-      <c r="D47" s="134"/>
-      <c r="E47" s="134"/>
-      <c r="F47" s="134"/>
-      <c r="G47" s="134"/>
-      <c r="H47" s="134"/>
-      <c r="I47" s="134"/>
-      <c r="J47" s="134"/>
-      <c r="K47" s="134"/>
-      <c r="L47" s="134"/>
-      <c r="M47" s="134"/>
-      <c r="N47" s="134"/>
-      <c r="O47" s="134"/>
-      <c r="P47" s="134"/>
-      <c r="Q47" s="134"/>
-      <c r="R47" s="134"/>
-      <c r="S47" s="135"/>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C47" s="132"/>
+      <c r="D47" s="132"/>
+      <c r="E47" s="132"/>
+      <c r="F47" s="132"/>
+      <c r="G47" s="132"/>
+      <c r="H47" s="132"/>
+      <c r="I47" s="132"/>
+      <c r="J47" s="132"/>
+      <c r="K47" s="132"/>
+      <c r="L47" s="132"/>
+      <c r="M47" s="132"/>
+      <c r="N47" s="132"/>
+      <c r="O47" s="132"/>
+      <c r="P47" s="132"/>
+      <c r="Q47" s="132"/>
+      <c r="R47" s="132"/>
+      <c r="S47" s="133"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B48" s="26"/>
       <c r="C48" s="27"/>
       <c r="D48" s="27"/>
@@ -17789,42 +17735,42 @@
       <c r="O48" s="27"/>
       <c r="S48" s="28"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B49" s="26"/>
-      <c r="C49" s="136" t="s">
+      <c r="C49" s="130" t="s">
         <v>16</v>
       </c>
-      <c r="D49" s="136"/>
-      <c r="E49" s="136"/>
+      <c r="D49" s="130"/>
+      <c r="E49" s="130"/>
       <c r="F49" s="27"/>
       <c r="G49" s="27"/>
-      <c r="H49" s="136" t="s">
+      <c r="H49" s="130" t="s">
         <v>1</v>
       </c>
-      <c r="I49" s="136"/>
-      <c r="J49" s="136"/>
+      <c r="I49" s="130"/>
+      <c r="J49" s="130"/>
       <c r="K49" s="27"/>
-      <c r="L49" s="136" t="s">
+      <c r="L49" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="M49" s="136"/>
-      <c r="N49" s="136"/>
+      <c r="M49" s="130"/>
+      <c r="N49" s="130"/>
       <c r="O49" s="27"/>
-      <c r="P49" s="136" t="s">
+      <c r="P49" s="130" t="s">
         <v>219</v>
       </c>
-      <c r="Q49" s="136"/>
-      <c r="R49" s="136"/>
+      <c r="Q49" s="130"/>
+      <c r="R49" s="130"/>
       <c r="S49" s="28"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B50" s="26"/>
       <c r="C50" s="36" t="s">
         <v>207</v>
       </c>
       <c r="D50" s="103">
         <f>D6*2.5</f>
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="E50" s="36" t="s">
         <v>209</v>
@@ -17849,14 +17795,12 @@
       <c r="O50" s="27"/>
       <c r="S50" s="28"/>
     </row>
-    <row r="51" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B51" s="26"/>
       <c r="C51" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D51" s="66" t="s">
-        <v>39</v>
-      </c>
+      <c r="D51" s="66"/>
       <c r="E51" s="35"/>
       <c r="F51" s="27"/>
       <c r="G51" s="27"/>
@@ -17885,22 +17829,20 @@
       <c r="P51" s="73" t="s">
         <v>216</v>
       </c>
-      <c r="Q51" s="74">
-        <v>978</v>
-      </c>
+      <c r="Q51" s="74"/>
       <c r="R51" s="35" t="s">
         <v>218</v>
       </c>
       <c r="S51" s="28"/>
     </row>
-    <row r="52" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B52" s="26"/>
       <c r="C52" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D52" s="102">
+      <c r="D52" s="102" t="e">
         <f>VLOOKUP(D51,Table9[#All],2,FALSE)</f>
-        <v>2.5</v>
+        <v>#N/A</v>
       </c>
       <c r="E52" s="36" t="s">
         <v>13</v>
@@ -17932,23 +17874,19 @@
       <c r="P52" s="73" t="s">
         <v>220</v>
       </c>
-      <c r="Q52" s="74">
-        <v>790</v>
-      </c>
+      <c r="Q52" s="74"/>
       <c r="R52" s="36" t="s">
         <v>218</v>
       </c>
       <c r="S52" s="28"/>
     </row>
-    <row r="53" spans="1:21" s="64" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" s="64" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="60"/>
       <c r="B53" s="61"/>
       <c r="C53" s="62" t="s">
         <v>210</v>
       </c>
-      <c r="D53" s="71">
-        <v>29</v>
-      </c>
+      <c r="D53" s="71"/>
       <c r="E53" s="36" t="s">
         <v>18</v>
       </c>
@@ -17973,9 +17911,7 @@
       <c r="P53" s="73" t="s">
         <v>217</v>
       </c>
-      <c r="Q53" s="74">
-        <v>665</v>
-      </c>
+      <c r="Q53" s="74"/>
       <c r="R53" s="36" t="s">
         <v>218</v>
       </c>
@@ -17983,7 +17919,7 @@
       <c r="T53" s="60"/>
       <c r="U53" s="60"/>
     </row>
-    <row r="54" spans="1:21" s="64" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:21" s="64" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="60"/>
       <c r="B54" s="29"/>
       <c r="C54" s="59"/>
@@ -18006,7 +17942,7 @@
       <c r="T54" s="60"/>
       <c r="U54" s="60"/>
     </row>
-    <row r="55" spans="1:21" s="64" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" s="64" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="60"/>
       <c r="B55" s="27"/>
       <c r="C55" s="27"/>
@@ -18029,7 +17965,7 @@
       <c r="T55" s="60"/>
       <c r="U55" s="60"/>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B56" s="27"/>
       <c r="C56" s="27"/>
       <c r="D56" s="27"/>
@@ -18045,19 +17981,19 @@
       <c r="N56" s="27"/>
       <c r="O56" s="27"/>
     </row>
-    <row r="57" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="2:15" s="27" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="2:15" s="27" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="2:15" s="27" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="2:15" s="27" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="2:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="58" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="59" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="1:21" s="27" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:15" s="27" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="66" spans="2:15" s="27" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="67" spans="2:15" s="27" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="68" spans="2:15" s="27" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:15" s="27" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B69" s="23"/>
       <c r="C69" s="23"/>
       <c r="D69" s="23"/>
@@ -18073,7 +18009,7 @@
       <c r="N69" s="23"/>
       <c r="O69" s="23"/>
     </row>
-    <row r="70" spans="2:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:15" s="27" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B70" s="23"/>
       <c r="C70" s="23"/>
       <c r="D70" s="23"/>
@@ -18091,11 +18027,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="P49:R49"/>
-    <mergeCell ref="B47:S47"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="L49:N49"/>
-    <mergeCell ref="C49:E49"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="B20:O20"/>
@@ -18104,6 +18035,11 @@
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="L22:N22"/>
+    <mergeCell ref="P49:R49"/>
+    <mergeCell ref="B47:S47"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="L49:N49"/>
+    <mergeCell ref="C49:E49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -18168,9 +18104,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B956EFC-C7D2-4042-961D-0867141FF08C}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="8.85546875" style="23"/>
+    <col min="1" max="16384" width="8.88671875" style="23"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18181,19 +18117,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2DD51B9-7836-448E-A643-9875AFE37E00}">
   <dimension ref="B2:L47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" customWidth="1"/>
-    <col min="6" max="6" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" customWidth="1"/>
+    <col min="6" max="6" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="B2" s="86" t="s">
         <v>233</v>
       </c>
@@ -18207,7 +18143,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>63</v>
       </c>
@@ -18234,7 +18170,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
         <v>66</v>
       </c>
@@ -18259,19 +18195,19 @@
       </c>
       <c r="K4" s="10">
         <f>'Inputs Residential &amp; Mixed-Use'!D23</f>
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="10" t="str">
+      <c r="C5" s="10">
         <f>'Inputs Residential &amp; Mixed-Use'!I6</f>
-        <v>21 Melbourne</v>
+        <v>0</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>69</v>
@@ -18280,9 +18216,9 @@
       <c r="F5" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="G5" s="10" t="str">
+      <c r="G5" s="10">
         <f>'Inputs Residential &amp; Mixed-Use'!I6</f>
-        <v>21 Melbourne</v>
+        <v>0</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>69</v>
@@ -18290,21 +18226,21 @@
       <c r="J5" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="K5" s="10" t="str">
+      <c r="K5" s="10">
         <f>'Inputs Residential &amp; Mixed-Use'!I6</f>
-        <v>21 Melbourne</v>
+        <v>0</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="10" t="e">
         <f>VLOOKUP('Inputs Residential &amp; Mixed-Use'!I6,Table11[#All],MATCH(C4,'Drop down'!I3:M3,0),FALSE)</f>
-        <v>199</v>
+        <v>#N/A</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>49</v>
@@ -18313,9 +18249,9 @@
       <c r="F6" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="10" t="e">
         <f>VLOOKUP('Inputs Residential &amp; Mixed-Use'!I6,Table11[#All],MATCH(G4,'Drop down'!I3:M3,0),FALSE)</f>
-        <v>62</v>
+        <v>#N/A</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>49</v>
@@ -18325,13 +18261,13 @@
       </c>
       <c r="K6" s="10">
         <f>'Inputs Residential &amp; Mixed-Use'!D24</f>
-        <v>51.2</v>
+        <v>0</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -18342,13 +18278,13 @@
       </c>
       <c r="K7" s="11">
         <f>'Inputs Residential &amp; Mixed-Use'!D25</f>
-        <v>17.899999999999999</v>
+        <v>0</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>72</v>
       </c>
@@ -18379,7 +18315,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -18396,13 +18332,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="14" t="e">
         <f>((C6*0.2777777778)*'Inputs Residential &amp; Mixed-Use'!D7*'Inputs Residential &amp; Mixed-Use'!D6)/C9</f>
-        <v>16164.867326995585</v>
+        <v>#N/A</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>71</v>
@@ -18411,9 +18347,9 @@
       <c r="F12" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="14" t="e">
         <f>((G6*0.2777777778)*'Inputs Residential &amp; Mixed-Use'!D7*'Inputs Residential &amp; Mixed-Use'!D6)/G9</f>
-        <v>5036.2903229835483</v>
+        <v>#N/A</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>71</v>
@@ -18424,13 +18360,13 @@
       </c>
       <c r="K12" s="14">
         <f>(((K6*0.2777777778)*'Inputs Residential &amp; Mixed-Use'!D7*'Inputs Residential &amp; Mixed-Use'!D6)/K9)+(((K7*0.2777777778)*'Inputs Residential &amp; Mixed-Use'!D7*'Inputs Residential &amp; Mixed-Use'!D6)/K10)</f>
-        <v>5613.0267954542451</v>
+        <v>0</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="5" t="s">
         <v>75</v>
       </c>
@@ -18457,7 +18393,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
         <v>109</v>
       </c>
@@ -18488,7 +18424,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
         <v>78</v>
       </c>
@@ -18518,13 +18454,13 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
         <v>80</v>
       </c>
       <c r="C18" s="14">
         <f>(C15/1000)*C16*365*'Inputs Residential &amp; Mixed-Use'!D7*'Inputs Residential &amp; Mixed-Use'!D6</f>
-        <v>13235.370967741936</v>
+        <v>0</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>71</v>
@@ -18535,7 +18471,7 @@
       </c>
       <c r="G18" s="14">
         <f>(G15/1000)*G16*365*'Inputs Residential &amp; Mixed-Use'!D7*'Inputs Residential &amp; Mixed-Use'!D6</f>
-        <v>13235.370967741936</v>
+        <v>0</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>71</v>
@@ -18546,13 +18482,13 @@
       </c>
       <c r="K18" s="14">
         <f>(K15/1000)*K16*365*'Inputs Residential &amp; Mixed-Use'!D7*'Inputs Residential &amp; Mixed-Use'!D6</f>
-        <v>13235.370967741936</v>
+        <v>0</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="9" t="s">
         <v>82</v>
       </c>
@@ -18579,7 +18515,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
         <v>83</v>
       </c>
@@ -18610,7 +18546,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
         <v>85</v>
       </c>
@@ -18640,7 +18576,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
         <v>86</v>
       </c>
@@ -18670,13 +18606,13 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
         <v>87</v>
       </c>
       <c r="C25" s="14">
         <f>((C21/1000)*C22*'Inputs Residential &amp; Mixed-Use'!D6*('Inputs Residential &amp; Mixed-Use'!D7*0.7)*365)+((C21/1000)*C23*'Inputs Residential &amp; Mixed-Use'!D6*('Inputs Residential &amp; Mixed-Use'!D7*0.3)*365)</f>
-        <v>14889.792338709674</v>
+        <v>0</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>71</v>
@@ -18687,7 +18623,7 @@
       </c>
       <c r="G25" s="14">
         <f>((G21/1000)*G22*'Inputs Residential &amp; Mixed-Use'!D6*('Inputs Residential &amp; Mixed-Use'!D7*0.7)*365)+((G21/1000)*G23*'Inputs Residential &amp; Mixed-Use'!D6*('Inputs Residential &amp; Mixed-Use'!D7*0.3)*365)</f>
-        <v>14889.792338709674</v>
+        <v>0</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>71</v>
@@ -18698,13 +18634,13 @@
       </c>
       <c r="K25" s="14">
         <f>((K21/1000)*K22*'Inputs Residential &amp; Mixed-Use'!D6*('Inputs Residential &amp; Mixed-Use'!D7*0.7)*365)+((K21/1000)*K23*'Inputs Residential &amp; Mixed-Use'!D6*('Inputs Residential &amp; Mixed-Use'!D7*0.3)*365)</f>
-        <v>11911.833870967743</v>
+        <v>0</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="9" t="s">
         <v>89</v>
       </c>
@@ -18731,13 +18667,13 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="6" t="s">
         <v>90</v>
       </c>
       <c r="C28" s="10">
         <f>'Inputs Residential &amp; Mixed-Use'!D50*60*365*1.25</f>
-        <v>1026562.5</v>
+        <v>0</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>91</v>
@@ -18748,7 +18684,7 @@
       </c>
       <c r="G28" s="10">
         <f>'Inputs Residential &amp; Mixed-Use'!D50*60*365</f>
-        <v>821250</v>
+        <v>0</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>91</v>
@@ -18758,13 +18694,13 @@
       </c>
       <c r="K28" s="10">
         <f>G28*(1-('Inputs Residential &amp; Mixed-Use'!D53/100))</f>
-        <v>583087.5</v>
+        <v>0</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="6" t="s">
         <v>93</v>
       </c>
@@ -18794,7 +18730,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="s">
         <v>95</v>
       </c>
@@ -18824,7 +18760,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
         <v>96</v>
       </c>
@@ -18854,13 +18790,13 @@
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="s">
         <v>98</v>
       </c>
       <c r="C32" s="10">
         <f>(C28*C31*(C30-C29))</f>
-        <v>193373.57812499997</v>
+        <v>0</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>201</v>
@@ -18871,7 +18807,7 @@
       </c>
       <c r="G32" s="10">
         <f>(G28*G31*(G30-G29))/3.6</f>
-        <v>42971.906249999993</v>
+        <v>0</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>71</v>
@@ -18881,13 +18817,13 @@
       </c>
       <c r="K32" s="10">
         <f>(K28*K31*(K30-K29))/3.6</f>
-        <v>30510.053437499999</v>
+        <v>0</v>
       </c>
       <c r="L32" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
@@ -18896,7 +18832,7 @@
       <c r="J33" s="6"/>
       <c r="L33" s="6"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="6" t="s">
         <v>100</v>
       </c>
@@ -18919,15 +18855,15 @@
       <c r="J34" t="s">
         <v>101</v>
       </c>
-      <c r="K34" s="10">
+      <c r="K34" s="10" t="e">
         <f>'Inputs Residential &amp; Mixed-Use'!D52</f>
-        <v>2.5</v>
+        <v>#N/A</v>
       </c>
       <c r="L34" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="6"/>
       <c r="C35" s="88"/>
       <c r="D35" s="6"/>
@@ -18943,13 +18879,13 @@
       </c>
       <c r="L35" s="6"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="7" t="s">
         <v>102</v>
       </c>
       <c r="C37" s="14">
         <f>C32/C34</f>
-        <v>322289.29687499994</v>
+        <v>0</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>201</v>
@@ -18960,7 +18896,7 @@
       </c>
       <c r="G37" s="14">
         <f>G32/G34</f>
-        <v>42971.906249999993</v>
+        <v>0</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>71</v>
@@ -18969,15 +18905,15 @@
       <c r="J37" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="K37" s="14">
+      <c r="K37" s="14" t="e">
         <f>IF('Inputs Residential &amp; Mixed-Use'!D51="Heat pump",(K32/K34)*(1+K35),(K32/K34))</f>
-        <v>13424.423512500001</v>
+        <v>#N/A</v>
       </c>
       <c r="L37" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B39" s="9" t="s">
         <v>108</v>
       </c>
@@ -18997,7 +18933,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="s">
         <v>188</v>
       </c>
@@ -19015,10 +18951,10 @@
       </c>
       <c r="K40" t="str">
         <f>IF('Inputs Residential &amp; Mixed-Use'!D32="Gas","Gas","Electric")</f>
-        <v>Gas</v>
-      </c>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+        <v>Electric</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>111</v>
       </c>
@@ -19043,14 +18979,14 @@
       </c>
       <c r="K41" s="10">
         <f>VLOOKUP('Inputs Residential &amp; Mixed-Use'!D32,Table10[#All],2,FALSE)</f>
-        <v>6</v>
+        <v>0.35</v>
       </c>
       <c r="L41" t="str">
         <f>IF(K40="Gas", "MJ/yr", "kWh/yr")</f>
-        <v>MJ/yr</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+        <v>kWh/yr</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>78</v>
       </c>
@@ -19079,13 +19015,13 @@
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B44" s="8" t="s">
         <v>113</v>
       </c>
       <c r="C44" s="14">
         <f>C41*C42*365*'Inputs Residential &amp; Mixed-Use'!D6</f>
-        <v>49275</v>
+        <v>0</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>201</v>
@@ -19096,7 +19032,7 @@
       </c>
       <c r="G44" s="14">
         <f>G41*G42*365*'Inputs Residential &amp; Mixed-Use'!D6</f>
-        <v>3161.8125</v>
+        <v>0</v>
       </c>
       <c r="H44" s="8" t="s">
         <v>71</v>
@@ -19107,14 +19043,14 @@
       </c>
       <c r="K44" s="14">
         <f>IF(K40="Electric",(K41*K42*365*'Inputs Residential &amp; Mixed-Use'!D6),(K41*K42*'Inputs Residential &amp; Mixed-Use'!D6*365))</f>
-        <v>49275</v>
+        <v>0</v>
       </c>
       <c r="L44" s="8" t="str">
         <f>IF(K40="Gas", "MJ/yr", "kWh/yr")</f>
-        <v>MJ/yr</v>
-      </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+        <v>kWh/yr</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B46" s="9" t="s">
         <v>116</v>
       </c>
@@ -19122,13 +19058,13 @@
         <v>116</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B47" s="8" t="s">
         <v>117</v>
       </c>
       <c r="C47" s="14">
         <f>G47</f>
-        <v>8590</v>
+        <v>0</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>71</v>
@@ -19139,7 +19075,7 @@
       </c>
       <c r="G47" s="14">
         <f>'Inputs Residential &amp; Mixed-Use'!D33</f>
-        <v>8590</v>
+        <v>0</v>
       </c>
       <c r="H47" s="8" t="s">
         <v>71</v>
@@ -19150,7 +19086,7 @@
       </c>
       <c r="K47" s="14">
         <f>'Inputs Residential &amp; Mixed-Use'!D34</f>
-        <v>6013</v>
+        <v>0</v>
       </c>
       <c r="L47" s="8" t="s">
         <v>71</v>
@@ -19166,15 +19102,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07E03289-C83F-4482-8B26-9A879D6E09A4}">
   <dimension ref="B2:H46"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="B2" s="89" t="s">
         <v>118</v>
       </c>
@@ -19185,7 +19121,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>200</v>
       </c>
@@ -19202,13 +19138,13 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C4" s="10">
         <f>'Inputs Residential &amp; Mixed-Use'!I7</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>69</v>
@@ -19218,19 +19154,19 @@
       </c>
       <c r="G4" s="10">
         <f>'Inputs Residential &amp; Mixed-Use'!I7</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="10" t="e">
         <f>VLOOKUP(C4,Table12[#All],2,FALSE)</f>
-        <v>28.22345208242939</v>
+        <v>#N/A</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>132</v>
@@ -19238,15 +19174,15 @@
       <c r="F5" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="10" t="e">
         <f>VLOOKUP(C4,Table12[#All],2,FALSE)*(1-('Inputs Residential &amp; Mixed-Use'!I23/100))</f>
-        <v>28.22345208242939</v>
+        <v>#N/A</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>72</v>
       </c>
@@ -19267,13 +19203,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="14" t="e">
         <f>IF(SUM('Inputs Residential &amp; Mixed-Use'!I32:I35)=0,(C5/C7)*'Inputs Residential &amp; Mixed-Use'!D8,(('Inputs Residential &amp; Mixed-Use'!I32+'Inputs Residential &amp; Mixed-Use'!I33)*'Inputs Residential &amp; Mixed-Use'!D8))</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>71</v>
@@ -19282,15 +19218,15 @@
       <c r="F9" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="14" t="e">
         <f>IF(SUM('Inputs Residential &amp; Mixed-Use'!I39:I42)=0,(G5/G7)*'Inputs Residential &amp; Mixed-Use'!D8,(('Inputs Residential &amp; Mixed-Use'!I39+'Inputs Residential &amp; Mixed-Use'!I40)*'Inputs Residential &amp; Mixed-Use'!D8))</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" s="6"/>
       <c r="C10" s="20"/>
       <c r="D10" s="6"/>
@@ -19298,7 +19234,7 @@
       <c r="G10" s="20"/>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="2:8" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>202</v>
       </c>
@@ -19315,7 +19251,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>68</v>
       </c>
@@ -19337,7 +19273,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>70</v>
       </c>
@@ -19359,7 +19295,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
         <v>72</v>
       </c>
@@ -19380,7 +19316,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>73</v>
       </c>
@@ -19403,7 +19339,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>182</v>
       </c>
@@ -19412,14 +19348,14 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="1"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
         <v>183</v>
       </c>
@@ -19442,7 +19378,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="9" t="s">
         <v>82</v>
       </c>
@@ -19459,7 +19395,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
         <v>83</v>
       </c>
@@ -19480,7 +19416,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
         <v>133</v>
       </c>
@@ -19500,7 +19436,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="7" t="s">
         <v>87</v>
       </c>
@@ -19523,7 +19459,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="9" t="s">
         <v>89</v>
       </c>
@@ -19540,7 +19476,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="s">
         <v>90</v>
       </c>
@@ -19562,7 +19498,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
         <v>93</v>
       </c>
@@ -19582,7 +19518,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="s">
         <v>95</v>
       </c>
@@ -19602,7 +19538,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="s">
         <v>96</v>
       </c>
@@ -19622,7 +19558,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" s="6" t="s">
         <v>98</v>
       </c>
@@ -19644,13 +19580,13 @@
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="6"/>
       <c r="D35" s="6"/>
       <c r="F35" s="6"/>
       <c r="H35" s="6"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="s">
         <v>100</v>
       </c>
@@ -19671,7 +19607,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="7" t="s">
         <v>102</v>
       </c>
@@ -19694,7 +19630,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B40" s="9" t="s">
         <v>108</v>
       </c>
@@ -19705,7 +19641,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="6" t="s">
         <v>230</v>
       </c>
@@ -19715,12 +19651,12 @@
       <c r="F41" t="s">
         <v>230</v>
       </c>
-      <c r="G41" t="str">
+      <c r="G41">
         <f>'Inputs Residential &amp; Mixed-Use'!I27</f>
-        <v>None</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>190</v>
       </c>
@@ -19735,7 +19671,7 @@
         <v>Electric</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>111</v>
       </c>
@@ -19749,16 +19685,16 @@
       <c r="F43" t="s">
         <v>110</v>
       </c>
-      <c r="G43" s="10">
+      <c r="G43" s="10" t="e">
         <f>VLOOKUP(G41,Table10[#All],3,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="H43" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="H43" t="e">
         <f>VLOOKUP(G41,Table10[#All],4,FALSE)</f>
-        <v>kW/h</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>78</v>
       </c>
@@ -19778,13 +19714,13 @@
         <v>112</v>
       </c>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B46" s="8" t="s">
         <v>113</v>
       </c>
       <c r="C46" s="14">
         <f>IF('Inputs Residential &amp; Mixed-Use'!I27="None",0,(C43*C44*365))</f>
-        <v>0</v>
+        <v>63072.000000000007</v>
       </c>
       <c r="D46" s="8" t="str">
         <f>IF(C42="Gas","MJ/yr","kWh/yr")</f>
@@ -19794,9 +19730,9 @@
       <c r="F46" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="G46" s="14">
+      <c r="G46" s="14" t="e">
         <f>IF(G42="Gas",(G43*G44*365),(G43*G44*365))</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="H46" s="8" t="str">
         <f>IF(G42="Gas","MJ/yr","kWh/yr")</f>
@@ -19812,15 +19748,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53EF2642-E153-4AED-9FB0-35F180787D0A}">
   <dimension ref="B3:H44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>200</v>
       </c>
@@ -19837,13 +19773,13 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C4" s="10">
         <f>'Inputs Residential &amp; Mixed-Use'!I7</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>69</v>
@@ -19853,19 +19789,19 @@
       </c>
       <c r="G4" s="10">
         <f>'Inputs Residential &amp; Mixed-Use'!I7</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="10" t="e">
         <f>VLOOKUP(C4,Table12[#All],3,FALSE)</f>
-        <v>16.7</v>
+        <v>#N/A</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>132</v>
@@ -19873,15 +19809,15 @@
       <c r="F5" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="10" t="e">
         <f>VLOOKUP(C4,Table12[#All],3,FALSE)*(1-('Inputs Residential &amp; Mixed-Use'!M23/100))</f>
-        <v>16.7</v>
+        <v>#N/A</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>72</v>
       </c>
@@ -19902,13 +19838,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="14" t="e">
         <f>IF(SUM('Inputs Residential &amp; Mixed-Use'!M31:M34)=0,(C5*'Inputs Residential &amp; Mixed-Use'!D9)/C7,(('Inputs Residential &amp; Mixed-Use'!M31+'Inputs Residential &amp; Mixed-Use'!M32)*'Inputs Residential &amp; Mixed-Use'!D9))</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>71</v>
@@ -19917,15 +19853,15 @@
       <c r="F9" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="14" t="e">
         <f>IF(SUM('Inputs Residential &amp; Mixed-Use'!M31:M34)=0,(G5*'Inputs Residential &amp; Mixed-Use'!D9)/G7,(('Inputs Residential &amp; Mixed-Use'!M38+'Inputs Residential &amp; Mixed-Use'!M39)*'Inputs Residential &amp; Mixed-Use'!D9))</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>202</v>
       </c>
@@ -19942,7 +19878,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>68</v>
       </c>
@@ -19964,7 +19900,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>70</v>
       </c>
@@ -19986,7 +19922,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
         <v>72</v>
       </c>
@@ -20007,7 +19943,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>73</v>
       </c>
@@ -20030,7 +19966,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>182</v>
       </c>
@@ -20039,14 +19975,14 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="1"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
         <v>183</v>
       </c>
@@ -20069,7 +20005,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="5" t="s">
         <v>75</v>
       </c>
@@ -20086,7 +20022,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
         <v>109</v>
       </c>
@@ -20106,7 +20042,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
         <v>78</v>
       </c>
@@ -20126,7 +20062,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="7" t="s">
         <v>80</v>
       </c>
@@ -20149,7 +20085,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="9" t="s">
         <v>82</v>
       </c>
@@ -20166,7 +20102,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="s">
         <v>83</v>
       </c>
@@ -20187,7 +20123,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
         <v>133</v>
       </c>
@@ -20207,7 +20143,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="7" t="s">
         <v>87</v>
       </c>
@@ -20230,7 +20166,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="9" t="s">
         <v>89</v>
       </c>
@@ -20247,7 +20183,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="s">
         <v>90</v>
       </c>
@@ -20269,7 +20205,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="s">
         <v>93</v>
       </c>
@@ -20289,7 +20225,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="6" t="s">
         <v>95</v>
       </c>
@@ -20309,7 +20245,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B39" s="6" t="s">
         <v>96</v>
       </c>
@@ -20329,7 +20265,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="s">
         <v>98</v>
       </c>
@@ -20351,13 +20287,13 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="6"/>
       <c r="D41" s="6"/>
       <c r="F41" s="6"/>
       <c r="H41" s="6"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B42" s="6" t="s">
         <v>100</v>
       </c>
@@ -20378,7 +20314,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B44" s="7" t="s">
         <v>102</v>
       </c>
@@ -20409,15 +20345,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2DB42DD-43C1-4867-805D-9608F5002492}">
   <dimension ref="B2:H20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>63</v>
       </c>
@@ -20434,13 +20370,13 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C3" s="10">
         <f>'Inputs Residential &amp; Mixed-Use'!I7</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>69</v>
@@ -20450,19 +20386,19 @@
       </c>
       <c r="G3" s="10">
         <f>'Inputs Residential &amp; Mixed-Use'!I7</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="10" t="e">
         <f>VLOOKUP(C3,Table12[#All],4,FALSE)</f>
-        <v>20</v>
+        <v>#N/A</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>132</v>
@@ -20470,15 +20406,15 @@
       <c r="F4" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="10" t="e">
         <f>VLOOKUP(C3,Table12[#All],4,FALSE)*(1-('Inputs Residential &amp; Mixed-Use'!M22/100))</f>
-        <v>20</v>
+        <v>#N/A</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>72</v>
       </c>
@@ -20499,13 +20435,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="14" t="e">
         <f>(C4*'Inputs Residential &amp; Mixed-Use'!D10)/C6</f>
-        <v>692.25806451612902</v>
+        <v>#N/A</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>71</v>
@@ -20514,15 +20450,15 @@
       <c r="F8" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="14" t="e">
         <f>(G4*'Inputs Residential &amp; Mixed-Use'!D10)/G6</f>
-        <v>692.25806451612902</v>
+        <v>#N/A</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="6"/>
       <c r="C9" s="20"/>
       <c r="D9" s="6"/>
@@ -20530,7 +20466,7 @@
       <c r="G9" s="20"/>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" s="9" t="s">
         <v>82</v>
       </c>
@@ -20547,7 +20483,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" s="6" t="s">
         <v>83</v>
       </c>
@@ -20567,7 +20503,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>133</v>
       </c>
@@ -20587,13 +20523,13 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
         <v>87</v>
       </c>
       <c r="C14" s="14">
         <f>(C11/1000)*365*C12*('Inputs Residential &amp; Mixed-Use'!D11+'Inputs Residential &amp; Mixed-Use'!D10)</f>
-        <v>8906.2919999999995</v>
+        <v>0</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>71</v>
@@ -20604,13 +20540,13 @@
       </c>
       <c r="G14" s="14">
         <f>(G11/1000)*365*G12*('Inputs Residential &amp; Mixed-Use'!D11+'Inputs Residential &amp; Mixed-Use'!D10)</f>
-        <v>8906.2919999999995</v>
+        <v>0</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>166</v>
       </c>
@@ -20621,13 +20557,13 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>167</v>
       </c>
       <c r="C17">
         <f>'Inputs Residential &amp; Mixed-Use'!D15</f>
-        <v>46.51</v>
+        <v>0</v>
       </c>
       <c r="D17" t="s">
         <v>164</v>
@@ -20637,35 +20573,35 @@
       </c>
       <c r="G17">
         <f>'Inputs Residential &amp; Mixed-Use'!D15</f>
-        <v>46.51</v>
+        <v>0</v>
       </c>
       <c r="H17" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>162</v>
       </c>
       <c r="C18">
         <f>'Inputs Residential &amp; Mixed-Use'!D14</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18" t="s">
         <v>162</v>
       </c>
       <c r="G18">
         <f>'Inputs Residential &amp; Mixed-Use'!D14</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
         <v>168</v>
       </c>
       <c r="C20" s="90">
         <f>(((110000*((C17/2)/1)*10)/3600)+0.07*24*365)*C18</f>
-        <v>15437.788888888888</v>
+        <v>0</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>71</v>
@@ -20674,7 +20610,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="90">
         <f>(((110000*((G17/2)/1)*10)/3600)+0.07*24*365)*G18</f>
-        <v>15437.788888888888</v>
+        <v>0</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>71</v>
@@ -20689,15 +20625,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C9AA639-308E-451F-8C9F-E88EF1CD0A9F}">
   <dimension ref="B2:H16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>170</v>
       </c>
@@ -20714,13 +20650,13 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>227</v>
       </c>
       <c r="C4" s="10">
         <f>'Inputs Residential &amp; Mixed-Use'!D12*42.33*(3212/8760)</f>
-        <v>5051.1542399999989</v>
+        <v>0</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>71</v>
@@ -20731,13 +20667,13 @@
       </c>
       <c r="G4" s="10">
         <f>'Inputs Residential &amp; Mixed-Use'!D12*42.33*(3212/8760)</f>
-        <v>5051.1542399999989</v>
+        <v>0</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="6"/>
       <c r="C5" s="20"/>
       <c r="D5" s="6"/>
@@ -20745,7 +20681,7 @@
       <c r="G5" s="20"/>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
         <v>171</v>
       </c>
@@ -20762,7 +20698,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>83</v>
       </c>
@@ -20782,7 +20718,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>133</v>
       </c>
@@ -20802,13 +20738,13 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>87</v>
       </c>
       <c r="C10" s="14">
         <f>(C7/1000)*C8*365*'Inputs Residential &amp; Mixed-Use'!D12</f>
-        <v>2375.712</v>
+        <v>0</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>71</v>
@@ -20819,13 +20755,13 @@
       </c>
       <c r="G10" s="14">
         <f>(G7/1000)*G8*365*'Inputs Residential &amp; Mixed-Use'!D12</f>
-        <v>2375.712</v>
+        <v>0</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="9" t="s">
         <v>172</v>
       </c>
@@ -20842,7 +20778,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>83</v>
       </c>
@@ -20862,7 +20798,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
         <v>133</v>
       </c>
@@ -20882,7 +20818,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
         <v>87</v>
       </c>
@@ -20914,38 +20850,38 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B637D33-37A1-4563-9D13-3C298E78B961}">
   <dimension ref="A2:AC70"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="32.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="13.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" customWidth="1"/>
-    <col min="13" max="13" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="13.7109375" customWidth="1"/>
-    <col min="18" max="18" width="32.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="13.7109375" customWidth="1"/>
-    <col min="23" max="23" width="32.42578125" customWidth="1"/>
-    <col min="24" max="26" width="13.7109375" customWidth="1"/>
-    <col min="28" max="29" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="13.5546875" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="13.6640625" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" customWidth="1"/>
+    <col min="13" max="13" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="13.6640625" customWidth="1"/>
+    <col min="18" max="18" width="32.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="13.6640625" customWidth="1"/>
+    <col min="23" max="23" width="32.44140625" customWidth="1"/>
+    <col min="24" max="26" width="13.6640625" customWidth="1"/>
+    <col min="28" max="29" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:29" x14ac:dyDescent="0.25">
-      <c r="H2" s="140" t="s">
+    <row r="2" spans="3:29" x14ac:dyDescent="0.3">
+      <c r="H2" s="137" t="s">
         <v>225</v>
       </c>
-      <c r="I2" s="140"/>
+      <c r="I2" s="137"/>
       <c r="J2" s="17">
         <v>0.86</v>
       </c>
       <c r="K2" t="s">
         <v>186</v>
       </c>
-      <c r="R2" s="141" t="s">
+      <c r="R2" s="138" t="s">
         <v>122</v>
       </c>
-      <c r="S2" s="141"/>
+      <c r="S2" s="138"/>
       <c r="T2" s="17">
         <v>0.28899999999999998</v>
       </c>
@@ -20962,21 +20898,21 @@
         <v>205</v>
       </c>
     </row>
-    <row r="3" spans="3:29" x14ac:dyDescent="0.25">
-      <c r="H3" s="140" t="s">
+    <row r="3" spans="3:29" x14ac:dyDescent="0.3">
+      <c r="H3" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="I3" s="140"/>
+      <c r="I3" s="137"/>
       <c r="J3" s="17">
         <v>5.1529999999999999E-2</v>
       </c>
       <c r="K3" t="s">
         <v>206</v>
       </c>
-      <c r="R3" s="141" t="s">
+      <c r="R3" s="138" t="s">
         <v>123</v>
       </c>
-      <c r="S3" s="141"/>
+      <c r="S3" s="138"/>
       <c r="T3" s="17">
         <f>T2+0.05</f>
         <v>0.33899999999999997</v>
@@ -20985,11 +20921,11 @@
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="3:29" x14ac:dyDescent="0.25">
-      <c r="H4" s="140" t="s">
+    <row r="4" spans="3:29" x14ac:dyDescent="0.3">
+      <c r="H4" s="137" t="s">
         <v>215</v>
       </c>
-      <c r="I4" s="140"/>
+      <c r="I4" s="137"/>
       <c r="J4" s="17">
         <v>0</v>
       </c>
@@ -20998,36 +20934,36 @@
       </c>
       <c r="T4" s="17"/>
     </row>
-    <row r="5" spans="3:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="3:29" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C6" s="137" t="s">
+    <row r="5" spans="3:29" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="3:29" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C6" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="138"/>
-      <c r="E6" s="138"/>
-      <c r="F6" s="138"/>
-      <c r="G6" s="138"/>
-      <c r="H6" s="138"/>
-      <c r="I6" s="138"/>
-      <c r="J6" s="138"/>
-      <c r="K6" s="138"/>
-      <c r="L6" s="138"/>
-      <c r="M6" s="138"/>
-      <c r="N6" s="138"/>
-      <c r="O6" s="138"/>
-      <c r="P6" s="138"/>
-      <c r="Q6" s="138"/>
-      <c r="R6" s="138"/>
-      <c r="S6" s="138"/>
-      <c r="T6" s="138"/>
-      <c r="U6" s="138"/>
-      <c r="V6" s="138"/>
-      <c r="W6" s="138"/>
-      <c r="X6" s="138"/>
-      <c r="Y6" s="138"/>
-      <c r="Z6" s="139"/>
-    </row>
-    <row r="7" spans="3:29" ht="45" x14ac:dyDescent="0.25">
+      <c r="D6" s="140"/>
+      <c r="E6" s="140"/>
+      <c r="F6" s="140"/>
+      <c r="G6" s="140"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="140"/>
+      <c r="K6" s="140"/>
+      <c r="L6" s="140"/>
+      <c r="M6" s="140"/>
+      <c r="N6" s="140"/>
+      <c r="O6" s="140"/>
+      <c r="P6" s="140"/>
+      <c r="Q6" s="140"/>
+      <c r="R6" s="140"/>
+      <c r="S6" s="140"/>
+      <c r="T6" s="140"/>
+      <c r="U6" s="140"/>
+      <c r="V6" s="140"/>
+      <c r="W6" s="140"/>
+      <c r="X6" s="140"/>
+      <c r="Y6" s="140"/>
+      <c r="Z6" s="141"/>
+    </row>
+    <row r="7" spans="3:29" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C7" s="37" t="s">
         <v>138</v>
       </c>
@@ -21037,9 +20973,9 @@
       <c r="E7" s="101" t="s">
         <v>236</v>
       </c>
-      <c r="F7" s="101" t="str">
+      <c r="F7" s="101">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
+        <v>0</v>
       </c>
       <c r="G7" s="15"/>
       <c r="H7" s="8" t="s">
@@ -21051,9 +20987,9 @@
       <c r="J7" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="K7" s="91" t="str">
+      <c r="K7" s="91">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
+        <v>0</v>
       </c>
       <c r="L7" s="15"/>
       <c r="M7" s="91" t="s">
@@ -21065,9 +21001,9 @@
       <c r="O7" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="P7" s="91" t="str">
+      <c r="P7" s="91">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
+        <v>0</v>
       </c>
       <c r="R7" s="8" t="s">
         <v>121</v>
@@ -21078,9 +21014,9 @@
       <c r="T7" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="U7" s="91" t="str">
+      <c r="U7" s="91">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
+        <v>0</v>
       </c>
       <c r="W7" s="8" t="s">
         <v>124</v>
@@ -21091,110 +21027,110 @@
       <c r="Y7" s="101" t="s">
         <v>236</v>
       </c>
-      <c r="Z7" s="101" t="str">
+      <c r="Z7" s="101">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
-      </c>
-    </row>
-    <row r="8" spans="3:29" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C8" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="15" t="e">
         <f>'Calculations Residential'!C12</f>
-        <v>16164.867326995585</v>
-      </c>
-      <c r="E8" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="E8" s="15" t="e">
         <f>'Calculations Residential'!G12</f>
-        <v>5036.2903229835483</v>
+        <v>#N/A</v>
       </c>
       <c r="F8" s="15">
         <f>'Calculations Residential'!K12</f>
-        <v>5613.0267954542451</v>
+        <v>0</v>
       </c>
       <c r="G8" s="15"/>
       <c r="H8" s="15" t="str">
         <f t="shared" ref="H8:H15" si="0">C8</f>
         <v>Heating &amp; Cooling</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="15" t="e">
         <f>(D8*$J$2)/1000</f>
-        <v>13.901785901216202</v>
-      </c>
-      <c r="J8" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="J8" s="15" t="e">
         <f>(E8*$J$2)/1000</f>
-        <v>4.3312096777658518</v>
+        <v>#N/A</v>
       </c>
       <c r="K8" s="15">
         <f>(F8*$J$2)/1000</f>
-        <v>4.827203044090651</v>
+        <v>0</v>
       </c>
       <c r="L8" s="15"/>
       <c r="M8" s="15" t="str">
         <f>H8</f>
         <v>Heating &amp; Cooling</v>
       </c>
-      <c r="N8" s="15">
+      <c r="N8" s="15" t="e">
         <f>I8</f>
-        <v>13.901785901216202</v>
-      </c>
-      <c r="O8" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="O8" s="15" t="e">
         <f t="shared" ref="O8:O13" si="1">(E8*$J$2)/1000</f>
-        <v>4.3312096777658518</v>
+        <v>#N/A</v>
       </c>
       <c r="P8" s="15">
         <f>IF('Inputs Residential &amp; Mixed-Use'!$D$17="Whole Development",((F8*$J$4)/1000),((F8*$J$2)/1000))</f>
-        <v>4.827203044090651</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="15"/>
       <c r="R8" t="str">
         <f t="shared" ref="R8:R15" si="2">C8</f>
         <v>Heating &amp; Cooling</v>
       </c>
-      <c r="S8" s="38">
+      <c r="S8" s="38" t="e">
         <f t="shared" ref="S8:T10" si="3">D8*$T$2</f>
-        <v>4671.6466575017239</v>
-      </c>
-      <c r="T8" s="38">
+        <v>#N/A</v>
+      </c>
+      <c r="T8" s="38" t="e">
         <f t="shared" si="3"/>
-        <v>1455.4879033422453</v>
+        <v>#N/A</v>
       </c>
       <c r="U8" s="38">
         <f>IF('Inputs Residential &amp; Mixed-Use'!$D$17="Whole Development",'Totals Residential &amp; Mixed-Use'!F8*$T$3, 'Totals Residential &amp; Mixed-Use'!F8*$T$2)</f>
-        <v>1622.1647438862767</v>
+        <v>0</v>
       </c>
       <c r="W8" t="str">
         <f>R8</f>
         <v>Heating &amp; Cooling</v>
       </c>
-      <c r="X8" s="39">
+      <c r="X8" s="39" t="e">
         <f>S8/'Inputs Residential &amp; Mixed-Use'!$D$6</f>
-        <v>311.44311050011493</v>
-      </c>
-      <c r="Y8" s="39">
+        <v>#N/A</v>
+      </c>
+      <c r="Y8" s="39" t="e">
         <f>T8/'Inputs Residential &amp; Mixed-Use'!$D$6</f>
-        <v>97.032526889483023</v>
-      </c>
-      <c r="Z8" s="40">
+        <v>#N/A</v>
+      </c>
+      <c r="Z8" s="40" t="e">
         <f>U8/'Inputs Residential &amp; Mixed-Use'!$D$6</f>
-        <v>108.14431625908512</v>
-      </c>
-    </row>
-    <row r="9" spans="3:29" x14ac:dyDescent="0.25">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C9" s="21" t="s">
         <v>126</v>
       </c>
       <c r="D9" s="15">
         <f>'Calculations Residential'!C18</f>
-        <v>13235.370967741936</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <f>'Calculations Residential'!G18</f>
-        <v>13235.370967741936</v>
+        <v>0</v>
       </c>
       <c r="F9" s="15">
         <f>'Calculations Residential'!K18</f>
-        <v>13235.370967741936</v>
+        <v>0</v>
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="15" t="str">
@@ -21203,15 +21139,15 @@
       </c>
       <c r="I9" s="15">
         <f>(D9*$J$2)/1000</f>
-        <v>11.382419032258065</v>
+        <v>0</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" ref="J9:K13" si="4">(E9*$J$2)/1000</f>
-        <v>11.382419032258065</v>
+        <v>0</v>
       </c>
       <c r="K9" s="15">
         <f t="shared" si="4"/>
-        <v>11.382419032258065</v>
+        <v>0</v>
       </c>
       <c r="L9" s="15"/>
       <c r="M9" s="15" t="str">
@@ -21220,15 +21156,15 @@
       </c>
       <c r="N9" s="15">
         <f>I9</f>
-        <v>11.382419032258065</v>
+        <v>0</v>
       </c>
       <c r="O9" s="15">
         <f t="shared" si="1"/>
-        <v>11.382419032258065</v>
+        <v>0</v>
       </c>
       <c r="P9" s="15">
         <f>IF('Inputs Residential &amp; Mixed-Use'!$D$17="Whole Development",((F9*$J$4)/1000),((F9*$J$2)/1000))</f>
-        <v>11.382419032258065</v>
+        <v>0</v>
       </c>
       <c r="R9" t="str">
         <f t="shared" si="2"/>
@@ -21236,50 +21172,50 @@
       </c>
       <c r="S9" s="38">
         <f t="shared" si="3"/>
-        <v>3825.0222096774191</v>
+        <v>0</v>
       </c>
       <c r="T9" s="38">
         <f t="shared" si="3"/>
-        <v>3825.0222096774191</v>
+        <v>0</v>
       </c>
       <c r="U9" s="38">
         <f>IF('Inputs Residential &amp; Mixed-Use'!$D$17="Whole Development",'Totals Residential &amp; Mixed-Use'!F9*$T$3, 'Totals Residential &amp; Mixed-Use'!F9*$T$2)</f>
-        <v>3825.0222096774191</v>
+        <v>0</v>
       </c>
       <c r="W9" t="str">
         <f t="shared" ref="W9:W15" si="6">R9</f>
         <v>Appliances</v>
       </c>
-      <c r="X9" s="39">
+      <c r="X9" s="39" t="e">
         <f>S9/'Inputs Residential &amp; Mixed-Use'!$D$6</f>
-        <v>255.00148064516128</v>
-      </c>
-      <c r="Y9" s="39">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y9" s="39" t="e">
         <f>T9/'Inputs Residential &amp; Mixed-Use'!$D$6</f>
-        <v>255.00148064516128</v>
-      </c>
-      <c r="Z9" s="40">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z9" s="40" t="e">
         <f>U9/'Inputs Residential &amp; Mixed-Use'!$D$6</f>
-        <v>255.00148064516128</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AB9" s="39"/>
       <c r="AC9" s="39"/>
     </row>
-    <row r="10" spans="3:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C10" s="21" t="s">
         <v>127</v>
       </c>
       <c r="D10" s="15">
         <f>'Calculations Residential'!C25</f>
-        <v>14889.792338709674</v>
+        <v>0</v>
       </c>
       <c r="E10" s="15">
         <f>'Calculations Residential'!G25</f>
-        <v>14889.792338709674</v>
+        <v>0</v>
       </c>
       <c r="F10" s="15">
         <f>'Calculations Residential'!K25</f>
-        <v>11911.833870967743</v>
+        <v>0</v>
       </c>
       <c r="G10" s="15"/>
       <c r="H10" s="15" t="str">
@@ -21288,15 +21224,15 @@
       </c>
       <c r="I10" s="15">
         <f>(D10*$J$2)/1000</f>
-        <v>12.80522141129032</v>
+        <v>0</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="4"/>
-        <v>12.80522141129032</v>
+        <v>0</v>
       </c>
       <c r="K10" s="15">
         <f t="shared" si="4"/>
-        <v>10.244177129032259</v>
+        <v>0</v>
       </c>
       <c r="L10" s="15"/>
       <c r="M10" s="15" t="str">
@@ -21305,15 +21241,15 @@
       </c>
       <c r="N10" s="15">
         <f>I10</f>
-        <v>12.80522141129032</v>
+        <v>0</v>
       </c>
       <c r="O10" s="15">
         <f t="shared" si="1"/>
-        <v>12.80522141129032</v>
+        <v>0</v>
       </c>
       <c r="P10" s="15">
         <f>IF('Inputs Residential &amp; Mixed-Use'!$D$17="Whole Development",((F10*$J$4)/1000),((F10*$J$2)/1000))</f>
-        <v>10.244177129032259</v>
+        <v>0</v>
       </c>
       <c r="R10" t="str">
         <f t="shared" si="2"/>
@@ -21321,50 +21257,50 @@
       </c>
       <c r="S10" s="38">
         <f t="shared" si="3"/>
-        <v>4303.1499858870957</v>
+        <v>0</v>
       </c>
       <c r="T10" s="38">
         <f t="shared" si="3"/>
-        <v>4303.1499858870957</v>
+        <v>0</v>
       </c>
       <c r="U10" s="38">
         <f>IF('Inputs Residential &amp; Mixed-Use'!$D$17="Whole Development",'Totals Residential &amp; Mixed-Use'!F10*$T$3, 'Totals Residential &amp; Mixed-Use'!F10*$T$2)</f>
-        <v>3442.5199887096774</v>
+        <v>0</v>
       </c>
       <c r="W10" t="str">
         <f t="shared" si="6"/>
         <v>Lighting</v>
       </c>
-      <c r="X10" s="39">
+      <c r="X10" s="39" t="e">
         <f>S10/'Inputs Residential &amp; Mixed-Use'!$D$6</f>
-        <v>286.87666572580639</v>
-      </c>
-      <c r="Y10" s="39">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y10" s="39" t="e">
         <f>T10/'Inputs Residential &amp; Mixed-Use'!$D$6</f>
-        <v>286.87666572580639</v>
-      </c>
-      <c r="Z10" s="40">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z10" s="40" t="e">
         <f>U10/'Inputs Residential &amp; Mixed-Use'!$D$6</f>
-        <v>229.50133258064517</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AB10" s="39"/>
       <c r="AC10" s="39"/>
     </row>
-    <row r="11" spans="3:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C11" s="21" t="s">
         <v>128</v>
       </c>
       <c r="D11" s="15">
         <f>'Calculations Residential'!C37/3.6</f>
-        <v>89524.804687499985</v>
+        <v>0</v>
       </c>
       <c r="E11" s="15">
         <f>'Calculations Residential'!G37</f>
-        <v>42971.906249999993</v>
-      </c>
-      <c r="F11" s="15">
+        <v>0</v>
+      </c>
+      <c r="F11" s="15" t="e">
         <f>'Calculations Residential'!K37</f>
-        <v>13424.423512500001</v>
+        <v>#N/A</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15" t="str">
@@ -21373,15 +21309,15 @@
       </c>
       <c r="I11" s="15">
         <f>(D11*3.6*$J$3)/1000</f>
-        <v>16.607567467968746</v>
+        <v>0</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="4"/>
-        <v>36.955839374999996</v>
-      </c>
-      <c r="K11" s="15">
+        <v>0</v>
+      </c>
+      <c r="K11" s="15" t="e">
         <f t="shared" si="4"/>
-        <v>11.54500422075</v>
+        <v>#N/A</v>
       </c>
       <c r="L11" s="15"/>
       <c r="M11" s="15" t="str">
@@ -21390,15 +21326,15 @@
       </c>
       <c r="N11" s="15">
         <f>I11</f>
-        <v>16.607567467968746</v>
+        <v>0</v>
       </c>
       <c r="O11" s="15">
         <f t="shared" si="1"/>
-        <v>36.955839374999996</v>
-      </c>
-      <c r="P11" s="15">
+        <v>0</v>
+      </c>
+      <c r="P11" s="15" t="e">
         <f>IF('Inputs Residential &amp; Mixed-Use'!$D$17="Whole Development",((F11*$J$4)/1000),((F11*$J$2)/1000))</f>
-        <v>11.54500422075</v>
+        <v>#N/A</v>
       </c>
       <c r="R11" t="str">
         <f t="shared" si="2"/>
@@ -21406,50 +21342,50 @@
       </c>
       <c r="S11" s="38">
         <f>D11*3.6*$Y$2</f>
-        <v>11280.125390624999</v>
+        <v>0</v>
       </c>
       <c r="T11" s="38">
         <f>E11*$T$2</f>
-        <v>12418.880906249997</v>
-      </c>
-      <c r="U11" s="38">
+        <v>0</v>
+      </c>
+      <c r="U11" s="38" t="e">
         <f>IF('Inputs Residential &amp; Mixed-Use'!$D$17="Whole Development",'Totals Residential &amp; Mixed-Use'!F11*$T$3, 'Totals Residential &amp; Mixed-Use'!F11*$T$2)</f>
-        <v>3879.6583951125003</v>
+        <v>#N/A</v>
       </c>
       <c r="W11" t="str">
         <f t="shared" si="6"/>
         <v>Hot Water</v>
       </c>
-      <c r="X11" s="39">
+      <c r="X11" s="39" t="e">
         <f>S11/'Inputs Residential &amp; Mixed-Use'!$D$6</f>
-        <v>752.00835937499994</v>
-      </c>
-      <c r="Y11" s="39">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y11" s="39" t="e">
         <f>T11/'Inputs Residential &amp; Mixed-Use'!$D$6</f>
-        <v>827.92539374999978</v>
-      </c>
-      <c r="Z11" s="40">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z11" s="40" t="e">
         <f>U11/'Inputs Residential &amp; Mixed-Use'!$D$6</f>
-        <v>258.64389300750003</v>
+        <v>#N/A</v>
       </c>
       <c r="AB11" s="39"/>
       <c r="AC11" s="39"/>
     </row>
-    <row r="12" spans="3:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C12" s="21" t="s">
         <v>42</v>
       </c>
       <c r="D12" s="15">
         <f>'Calculations Residential'!C44/3.6</f>
-        <v>13687.5</v>
+        <v>0</v>
       </c>
       <c r="E12" s="15">
         <f>'Calculations Residential'!G44</f>
-        <v>3161.8125</v>
+        <v>0</v>
       </c>
       <c r="F12" s="15">
         <f>IF('Calculations Residential'!K40="Gas",'Calculations Residential'!K44*0.277776,'Calculations Residential'!K44)</f>
-        <v>13687.412400000001</v>
+        <v>0</v>
       </c>
       <c r="G12" s="15"/>
       <c r="H12" s="15" t="str">
@@ -21458,15 +21394,15 @@
       </c>
       <c r="I12" s="15">
         <f>(D12*3.6*$J$3)/1000</f>
-        <v>2.5391407500000001</v>
+        <v>0</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="4"/>
-        <v>2.7191587500000001</v>
+        <v>0</v>
       </c>
       <c r="K12" s="15">
         <f t="shared" si="4"/>
-        <v>11.771174664</v>
+        <v>0</v>
       </c>
       <c r="L12" s="15"/>
       <c r="M12" s="15" t="str">
@@ -21475,15 +21411,15 @@
       </c>
       <c r="N12" s="15">
         <f>I12</f>
-        <v>2.5391407500000001</v>
+        <v>0</v>
       </c>
       <c r="O12" s="15">
         <f t="shared" si="1"/>
-        <v>2.7191587500000001</v>
+        <v>0</v>
       </c>
       <c r="P12" s="15">
         <f>IF('Inputs Residential &amp; Mixed-Use'!$D$17="Whole Development",((F12*$J$4)/1000),((F12*$J$2)/1000))</f>
-        <v>11.771174664</v>
+        <v>0</v>
       </c>
       <c r="R12" t="str">
         <f t="shared" si="2"/>
@@ -21491,48 +21427,48 @@
       </c>
       <c r="S12" s="38">
         <f>D12*3.6*$Y$2</f>
-        <v>1724.6250000000002</v>
+        <v>0</v>
       </c>
       <c r="T12" s="38">
         <f>E12*$T$2</f>
-        <v>913.76381249999997</v>
+        <v>0</v>
       </c>
       <c r="U12" s="38">
         <f>IF('Inputs Residential &amp; Mixed-Use'!$D$17="Whole Development",'Totals Residential &amp; Mixed-Use'!F12*$T$3, 'Totals Residential &amp; Mixed-Use'!F12*$T$2)</f>
-        <v>3955.6621835999999</v>
+        <v>0</v>
       </c>
       <c r="W12" t="str">
         <f t="shared" si="6"/>
         <v>Cooktops</v>
       </c>
-      <c r="X12" s="39">
+      <c r="X12" s="39" t="e">
         <f>S12/'Inputs Residential &amp; Mixed-Use'!$D$6</f>
-        <v>114.97500000000001</v>
-      </c>
-      <c r="Y12" s="39">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y12" s="39" t="e">
         <f>T12/'Inputs Residential &amp; Mixed-Use'!$D$6</f>
-        <v>60.917587499999996</v>
-      </c>
-      <c r="Z12" s="40">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z12" s="40" t="e">
         <f>U12/'Inputs Residential &amp; Mixed-Use'!$D$6</f>
-        <v>263.71081224</v>
-      </c>
-    </row>
-    <row r="13" spans="3:29" x14ac:dyDescent="0.25">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C13" s="21" t="s">
         <v>115</v>
       </c>
       <c r="D13" s="15">
         <f>'Calculations Residential'!C47</f>
-        <v>8590</v>
+        <v>0</v>
       </c>
       <c r="E13" s="15">
         <f>'Calculations Residential'!G47</f>
-        <v>8590</v>
+        <v>0</v>
       </c>
       <c r="F13" s="15">
         <f>'Calculations Residential'!K47</f>
-        <v>6013</v>
+        <v>0</v>
       </c>
       <c r="G13" s="15"/>
       <c r="H13" s="15" t="str">
@@ -21541,15 +21477,15 @@
       </c>
       <c r="I13" s="15">
         <f>(D13*$J$2)/1000</f>
-        <v>7.3873999999999995</v>
+        <v>0</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="4"/>
-        <v>7.3873999999999995</v>
+        <v>0</v>
       </c>
       <c r="K13" s="15">
         <f t="shared" si="4"/>
-        <v>5.1711800000000006</v>
+        <v>0</v>
       </c>
       <c r="L13" s="15"/>
       <c r="M13" s="15" t="str">
@@ -21558,15 +21494,15 @@
       </c>
       <c r="N13" s="15">
         <f>I13</f>
-        <v>7.3873999999999995</v>
+        <v>0</v>
       </c>
       <c r="O13" s="15">
         <f t="shared" si="1"/>
-        <v>7.3873999999999995</v>
+        <v>0</v>
       </c>
       <c r="P13" s="15">
         <f>IF('Inputs Residential &amp; Mixed-Use'!$D$17="Whole Development",((F13*$J$4)/1000),((F13*$J$2)/1000))</f>
-        <v>5.1711800000000006</v>
+        <v>0</v>
       </c>
       <c r="R13" t="str">
         <f t="shared" si="2"/>
@@ -21574,34 +21510,34 @@
       </c>
       <c r="S13" s="38">
         <f>D13*$T$2</f>
-        <v>2482.5099999999998</v>
+        <v>0</v>
       </c>
       <c r="T13" s="52">
         <f>E13*$T$2</f>
-        <v>2482.5099999999998</v>
+        <v>0</v>
       </c>
       <c r="U13" s="38">
         <f>IF('Inputs Residential &amp; Mixed-Use'!$D$17="Whole Development",'Totals Residential &amp; Mixed-Use'!F13*$T$3, 'Totals Residential &amp; Mixed-Use'!F13*$T$2)</f>
-        <v>1737.7569999999998</v>
+        <v>0</v>
       </c>
       <c r="W13" t="str">
         <f t="shared" si="6"/>
         <v>Clothes Drying</v>
       </c>
-      <c r="X13" s="39">
+      <c r="X13" s="39" t="e">
         <f>S13/'Inputs Residential &amp; Mixed-Use'!$D$6</f>
-        <v>165.50066666666666</v>
-      </c>
-      <c r="Y13" s="39">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y13" s="39" t="e">
         <f>T13/'Inputs Residential &amp; Mixed-Use'!$D$6</f>
-        <v>165.50066666666666</v>
-      </c>
-      <c r="Z13" s="40">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z13" s="40" t="e">
         <f>U13/'Inputs Residential &amp; Mixed-Use'!$D$6</f>
-        <v>115.85046666666666</v>
-      </c>
-    </row>
-    <row r="14" spans="3:29" x14ac:dyDescent="0.25">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C14" s="21"/>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
@@ -21635,100 +21571,100 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="3:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C15" s="80" t="s">
         <v>120</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="18" t="e">
         <f>SUM(D8:D13)</f>
-        <v>156092.33532094717</v>
-      </c>
-      <c r="E15" s="18">
+        <v>#N/A</v>
+      </c>
+      <c r="E15" s="18" t="e">
         <f>SUM(E8:E13)</f>
-        <v>87885.172379435156</v>
-      </c>
-      <c r="F15" s="18">
+        <v>#N/A</v>
+      </c>
+      <c r="F15" s="18" t="e">
         <f>SUM(F8:F13)</f>
-        <v>63885.067546663922</v>
+        <v>#N/A</v>
       </c>
       <c r="G15" s="43"/>
       <c r="H15" s="42" t="str">
         <f t="shared" si="0"/>
         <v>Total</v>
       </c>
-      <c r="I15" s="42">
+      <c r="I15" s="42" t="e">
         <f>SUM(I8:I13)</f>
-        <v>64.62353456273334</v>
-      </c>
-      <c r="J15" s="42">
+        <v>#N/A</v>
+      </c>
+      <c r="J15" s="42" t="e">
         <f>SUM(J8:J13)</f>
-        <v>75.581248246314232</v>
-      </c>
-      <c r="K15" s="42">
+        <v>#N/A</v>
+      </c>
+      <c r="K15" s="42" t="e">
         <f>SUM(K8:K13)</f>
-        <v>54.941158090130976</v>
+        <v>#N/A</v>
       </c>
       <c r="L15" s="42"/>
       <c r="M15" s="42" t="str">
         <f t="shared" si="5"/>
         <v>Total</v>
       </c>
-      <c r="N15" s="42">
+      <c r="N15" s="42" t="e">
         <f>SUM(N8:N13)</f>
-        <v>64.62353456273334</v>
-      </c>
-      <c r="O15" s="42">
+        <v>#N/A</v>
+      </c>
+      <c r="O15" s="42" t="e">
         <f>SUM(O8:O13)</f>
-        <v>75.581248246314232</v>
-      </c>
-      <c r="P15" s="42">
+        <v>#N/A</v>
+      </c>
+      <c r="P15" s="42" t="e">
         <f>SUM(P8:P13)</f>
-        <v>54.941158090130976</v>
+        <v>#N/A</v>
       </c>
       <c r="Q15" s="44"/>
       <c r="R15" s="45" t="str">
         <f t="shared" si="2"/>
         <v>Total</v>
       </c>
-      <c r="S15" s="46">
+      <c r="S15" s="46" t="e">
         <f>SUM(S8:S13)</f>
-        <v>28287.079243691234</v>
-      </c>
-      <c r="T15" s="46">
+        <v>#N/A</v>
+      </c>
+      <c r="T15" s="46" t="e">
         <f>SUM(T8:T13)</f>
-        <v>25398.814817656756</v>
-      </c>
-      <c r="U15" s="46">
+        <v>#N/A</v>
+      </c>
+      <c r="U15" s="46" t="e">
         <f>SUM(U8:U13)</f>
-        <v>18462.784520985875</v>
+        <v>#N/A</v>
       </c>
       <c r="V15" s="44"/>
       <c r="W15" s="45" t="str">
         <f t="shared" si="6"/>
         <v>Total</v>
       </c>
-      <c r="X15" s="47">
+      <c r="X15" s="47" t="e">
         <f>SUM(X8:X13)</f>
-        <v>1885.8052829127489</v>
-      </c>
-      <c r="Y15" s="47">
+        <v>#N/A</v>
+      </c>
+      <c r="Y15" s="47" t="e">
         <f>SUM(Y8:Y13)</f>
-        <v>1693.2543211771172</v>
-      </c>
-      <c r="Z15" s="48">
+        <v>#N/A</v>
+      </c>
+      <c r="Z15" s="48" t="e">
         <f>SUM(Z8:Z13)</f>
-        <v>1230.8523013990584</v>
-      </c>
-    </row>
-    <row r="16" spans="3:29" x14ac:dyDescent="0.25">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C16" s="119" t="s">
         <v>242</v>
       </c>
       <c r="D16" s="120"/>
       <c r="E16" s="121"/>
-      <c r="F16" s="122">
+      <c r="F16" s="122" t="e">
         <f>(E15-F15)</f>
-        <v>24000.104832771234</v>
+        <v>#N/A</v>
       </c>
       <c r="G16" s="15"/>
       <c r="H16" s="18"/>
@@ -21749,7 +21685,7 @@
       <c r="Y16" s="85"/>
       <c r="Z16" s="85"/>
     </row>
-    <row r="17" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E17" s="15"/>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
@@ -21765,40 +21701,40 @@
       <c r="W17" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="X17" s="100">
+      <c r="X17" s="100" t="e">
         <f>X15-Z15</f>
-        <v>654.95298151369047</v>
-      </c>
-      <c r="Y17" s="100">
+        <v>#N/A</v>
+      </c>
+      <c r="Y17" s="100" t="e">
         <f>Y15-Z15</f>
-        <v>462.40201977805873</v>
+        <v>#N/A</v>
       </c>
       <c r="Z17" s="85"/>
     </row>
-    <row r="18" spans="1:26" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C18" s="137" t="s">
+    <row r="18" spans="1:26" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C18" s="139" t="s">
         <v>130</v>
       </c>
-      <c r="D18" s="138"/>
-      <c r="E18" s="138"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="138"/>
-      <c r="H18" s="138"/>
-      <c r="I18" s="138"/>
-      <c r="J18" s="138"/>
-      <c r="K18" s="138"/>
-      <c r="L18" s="138"/>
-      <c r="M18" s="138"/>
-      <c r="N18" s="138"/>
-      <c r="O18" s="138"/>
-      <c r="P18" s="138"/>
-      <c r="Q18" s="138"/>
-      <c r="R18" s="138"/>
-      <c r="S18" s="138"/>
-      <c r="T18" s="138"/>
-      <c r="U18" s="139"/>
-    </row>
-    <row r="19" spans="1:26" ht="30" x14ac:dyDescent="0.25">
+      <c r="D18" s="140"/>
+      <c r="E18" s="140"/>
+      <c r="F18" s="140"/>
+      <c r="G18" s="140"/>
+      <c r="H18" s="140"/>
+      <c r="I18" s="140"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="140"/>
+      <c r="L18" s="140"/>
+      <c r="M18" s="140"/>
+      <c r="N18" s="140"/>
+      <c r="O18" s="140"/>
+      <c r="P18" s="140"/>
+      <c r="Q18" s="140"/>
+      <c r="R18" s="140"/>
+      <c r="S18" s="140"/>
+      <c r="T18" s="140"/>
+      <c r="U18" s="141"/>
+    </row>
+    <row r="19" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C19" s="37" t="s">
         <v>138</v>
       </c>
@@ -21806,9 +21742,9 @@
       <c r="E19" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="F19" s="91" t="str">
+      <c r="F19" s="91">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
+        <v>0</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="8" t="s">
@@ -21818,9 +21754,9 @@
       <c r="J19" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="K19" s="91" t="str">
+      <c r="K19" s="91">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
+        <v>0</v>
       </c>
       <c r="L19" s="15"/>
       <c r="M19" s="91" t="s">
@@ -21830,9 +21766,9 @@
       <c r="O19" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="P19" s="91" t="str">
+      <c r="P19" s="91">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
+        <v>0</v>
       </c>
       <c r="R19" s="8" t="s">
         <v>121</v>
@@ -21841,22 +21777,22 @@
       <c r="T19" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="U19" s="98" t="str">
+      <c r="U19" s="98">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C20" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="15" t="e">
         <f>'Calculations Communal'!C8</f>
-        <v>692.25806451612902</v>
-      </c>
-      <c r="F20" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="F20" s="15" t="e">
         <f>'Calculations Communal'!G8</f>
-        <v>692.25806451612902</v>
+        <v>#N/A</v>
       </c>
       <c r="G20" s="15"/>
       <c r="H20" s="15" t="str">
@@ -21864,13 +21800,13 @@
         <v>Heating &amp; Cooling</v>
       </c>
       <c r="I20" s="15"/>
-      <c r="J20" s="15">
+      <c r="J20" s="15" t="e">
         <f>E20*$J$2/1000</f>
-        <v>0.59534193548387104</v>
-      </c>
-      <c r="K20" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="K20" s="15" t="e">
         <f>(F20*$J$2)/1000</f>
-        <v>0.59534193548387104</v>
+        <v>#N/A</v>
       </c>
       <c r="L20" s="15"/>
       <c r="M20" s="15" t="str">
@@ -21878,38 +21814,38 @@
         <v>Heating &amp; Cooling</v>
       </c>
       <c r="N20" s="15"/>
-      <c r="O20" s="15">
+      <c r="O20" s="15" t="e">
         <f>E20*$J$2/1000</f>
-        <v>0.59534193548387104</v>
-      </c>
-      <c r="P20" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="P20" s="15" t="e">
         <f>IF('Inputs Residential &amp; Mixed-Use'!$D$17="Whole Development",F20*$J$4/1000, IF('Inputs Residential &amp; Mixed-Use'!$D$17="Base Building",F20*$J$4/1000,F20*$J$2/1000))</f>
-        <v>0.59534193548387104</v>
+        <v>#N/A</v>
       </c>
       <c r="R20" t="str">
         <f>C20</f>
         <v>Heating &amp; Cooling</v>
       </c>
-      <c r="T20" s="15">
+      <c r="T20" s="15" t="e">
         <f t="shared" ref="T20:U22" si="7">E20*$T$2</f>
-        <v>200.06258064516126</v>
-      </c>
-      <c r="U20" s="49">
+        <v>#N/A</v>
+      </c>
+      <c r="U20" s="49" t="e">
         <f t="shared" si="7"/>
-        <v>200.06258064516126</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C21" s="21" t="s">
         <v>127</v>
       </c>
       <c r="E21" s="15">
         <f>'Calculations Communal'!C14</f>
-        <v>8906.2919999999995</v>
+        <v>0</v>
       </c>
       <c r="F21" s="15">
         <f>'Calculations Communal'!G14</f>
-        <v>8906.2919999999995</v>
+        <v>0</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15" t="str">
@@ -21919,11 +21855,11 @@
       <c r="I21" s="15"/>
       <c r="J21" s="15">
         <f>E21*$J$2/1000</f>
-        <v>7.6594111199999997</v>
+        <v>0</v>
       </c>
       <c r="K21" s="15">
         <f>(F21*$J$2)/1000</f>
-        <v>7.6594111199999997</v>
+        <v>0</v>
       </c>
       <c r="L21" s="15"/>
       <c r="M21" s="15" t="str">
@@ -21933,11 +21869,11 @@
       <c r="N21" s="15"/>
       <c r="O21" s="15">
         <f>E21*$J$2/1000</f>
-        <v>7.6594111199999997</v>
+        <v>0</v>
       </c>
       <c r="P21" s="15">
         <f>IF('Inputs Residential &amp; Mixed-Use'!$D$17="Whole Development",F21*$J$4/1000, IF('Inputs Residential &amp; Mixed-Use'!$D$17="Base Building",F21*$J$4/1000,F21*$J$2/1000))</f>
-        <v>7.6594111199999997</v>
+        <v>0</v>
       </c>
       <c r="R21" t="str">
         <f>C21</f>
@@ -21945,24 +21881,24 @@
       </c>
       <c r="T21" s="15">
         <f t="shared" si="7"/>
-        <v>2573.9183879999996</v>
+        <v>0</v>
       </c>
       <c r="U21" s="49">
         <f t="shared" si="7"/>
-        <v>2573.9183879999996</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C22" s="21" t="s">
         <v>165</v>
       </c>
       <c r="E22" s="15">
         <f>'Calculations Communal'!C20</f>
-        <v>15437.788888888888</v>
+        <v>0</v>
       </c>
       <c r="F22" s="15">
         <f>'Calculations Communal'!G20</f>
-        <v>15437.788888888888</v>
+        <v>0</v>
       </c>
       <c r="G22" s="15"/>
       <c r="H22" s="15" t="str">
@@ -21972,11 +21908,11 @@
       <c r="I22" s="15"/>
       <c r="J22" s="15">
         <f>E22*$J$2/1000</f>
-        <v>13.276498444444444</v>
+        <v>0</v>
       </c>
       <c r="K22" s="15">
         <f>(F22*$J$2)/1000</f>
-        <v>13.276498444444444</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15"/>
       <c r="M22" s="15" t="str">
@@ -21986,11 +21922,11 @@
       <c r="N22" s="15"/>
       <c r="O22" s="15">
         <f>E22*$J$2/1000</f>
-        <v>13.276498444444444</v>
+        <v>0</v>
       </c>
       <c r="P22" s="15">
         <f>IF('Inputs Residential &amp; Mixed-Use'!$D$17="Whole Development",F22*$J$4/1000, IF('Inputs Residential &amp; Mixed-Use'!$D$17="Base Building",F22*$J$4/1000,F22*$J$2/1000))</f>
-        <v>13.276498444444444</v>
+        <v>0</v>
       </c>
       <c r="R22" t="str">
         <f>C22</f>
@@ -21998,51 +21934,51 @@
       </c>
       <c r="T22" s="15">
         <f t="shared" si="7"/>
-        <v>4461.5209888888885</v>
+        <v>0</v>
       </c>
       <c r="U22" s="49">
         <f t="shared" si="7"/>
-        <v>4461.5209888888885</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C23" s="41" t="s">
         <v>120</v>
       </c>
       <c r="D23" s="45"/>
       <c r="E23" s="42">
         <f>SUM(E21:E22)</f>
-        <v>24344.080888888886</v>
+        <v>0</v>
       </c>
       <c r="F23" s="42">
         <f>SUM(F21:F22)</f>
-        <v>24344.080888888886</v>
+        <v>0</v>
       </c>
       <c r="G23" s="42"/>
       <c r="H23" s="42" t="s">
         <v>120</v>
       </c>
       <c r="I23" s="42"/>
-      <c r="J23" s="42">
+      <c r="J23" s="42" t="e">
         <f>SUM(J20:J22)</f>
-        <v>21.531251499928317</v>
-      </c>
-      <c r="K23" s="42">
+        <v>#N/A</v>
+      </c>
+      <c r="K23" s="42" t="e">
         <f>SUM(K20:K22)</f>
-        <v>21.531251499928317</v>
+        <v>#N/A</v>
       </c>
       <c r="L23" s="42"/>
       <c r="M23" s="42" t="s">
         <v>120</v>
       </c>
       <c r="N23" s="42"/>
-      <c r="O23" s="42">
+      <c r="O23" s="42" t="e">
         <f>SUM(O20:O22)</f>
-        <v>21.531251499928317</v>
-      </c>
-      <c r="P23" s="42">
+        <v>#N/A</v>
+      </c>
+      <c r="P23" s="42" t="e">
         <f>SUM(P20:P22)</f>
-        <v>21.531251499928317</v>
+        <v>#N/A</v>
       </c>
       <c r="Q23" s="45"/>
       <c r="R23" s="44" t="str">
@@ -22050,16 +21986,16 @@
         <v>Total</v>
       </c>
       <c r="S23" s="44"/>
-      <c r="T23" s="42">
+      <c r="T23" s="42" t="e">
         <f>SUM(T20:T22)</f>
-        <v>7235.5019575340493</v>
-      </c>
-      <c r="U23" s="50">
+        <v>#N/A</v>
+      </c>
+      <c r="U23" s="50" t="e">
         <f>SUM(U20:U22)</f>
-        <v>7235.5019575340493</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E24" s="15"/>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
@@ -22073,30 +22009,30 @@
       <c r="O24" s="15"/>
       <c r="P24" s="15"/>
     </row>
-    <row r="25" spans="1:26" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C25" s="137" t="s">
+    <row r="25" spans="1:26" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C25" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="D25" s="138"/>
-      <c r="E25" s="138"/>
-      <c r="F25" s="138"/>
-      <c r="G25" s="138"/>
-      <c r="H25" s="138"/>
-      <c r="I25" s="138"/>
-      <c r="J25" s="138"/>
-      <c r="K25" s="138"/>
-      <c r="L25" s="138"/>
-      <c r="M25" s="138"/>
-      <c r="N25" s="138"/>
-      <c r="O25" s="138"/>
-      <c r="P25" s="138"/>
-      <c r="Q25" s="138"/>
-      <c r="R25" s="138"/>
-      <c r="S25" s="138"/>
-      <c r="T25" s="138"/>
-      <c r="U25" s="139"/>
-    </row>
-    <row r="26" spans="1:26" ht="30" x14ac:dyDescent="0.25">
+      <c r="D25" s="140"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="140"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="140"/>
+      <c r="I25" s="140"/>
+      <c r="J25" s="140"/>
+      <c r="K25" s="140"/>
+      <c r="L25" s="140"/>
+      <c r="M25" s="140"/>
+      <c r="N25" s="140"/>
+      <c r="O25" s="140"/>
+      <c r="P25" s="140"/>
+      <c r="Q25" s="140"/>
+      <c r="R25" s="140"/>
+      <c r="S25" s="140"/>
+      <c r="T25" s="140"/>
+      <c r="U25" s="141"/>
+    </row>
+    <row r="26" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C26" s="37" t="s">
         <v>138</v>
       </c>
@@ -22104,9 +22040,9 @@
       <c r="E26" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="F26" s="91" t="str">
+      <c r="F26" s="91">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
+        <v>0</v>
       </c>
       <c r="G26" s="8"/>
       <c r="H26" s="8" t="s">
@@ -22116,9 +22052,9 @@
       <c r="J26" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="K26" s="91" t="str">
+      <c r="K26" s="91">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
+        <v>0</v>
       </c>
       <c r="M26" s="91" t="s">
         <v>228</v>
@@ -22127,9 +22063,9 @@
       <c r="O26" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="P26" s="91" t="str">
+      <c r="P26" s="91">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
+        <v>0</v>
       </c>
       <c r="R26" s="8" t="s">
         <v>134</v>
@@ -22138,22 +22074,22 @@
       <c r="T26" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="U26" s="98" t="str">
+      <c r="U26" s="98">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C27" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="15" t="e">
         <f>'Calculations Retail'!C9</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="F27" s="15" t="e">
         <f>'Calculations Retail'!G9</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15" t="str">
@@ -22161,13 +22097,13 @@
         <v>Heating &amp; Cooling (Elec)</v>
       </c>
       <c r="I27" s="15"/>
-      <c r="J27" s="15">
+      <c r="J27" s="15" t="e">
         <f>(E27*$J$2)/1000</f>
-        <v>0</v>
-      </c>
-      <c r="K27" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="K27" s="15" t="e">
         <f>(F27*$J$2)/1000</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="L27" s="15"/>
       <c r="M27" s="15" t="str">
@@ -22175,28 +22111,28 @@
         <v>Heating &amp; Cooling (Elec)</v>
       </c>
       <c r="N27" s="15"/>
-      <c r="O27" s="15">
+      <c r="O27" s="15" t="e">
         <f>(E27*$J$2)/1000</f>
-        <v>0</v>
-      </c>
-      <c r="P27" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="P27" s="15" t="e">
         <f>IF('Inputs Residential &amp; Mixed-Use'!$D$17="Whole Development",((F27*$J$4)/1000),((F27*$J$2)/1000))</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="R27" t="str">
         <f>C27</f>
         <v>Heating &amp; Cooling (Elec)</v>
       </c>
-      <c r="T27" s="38">
+      <c r="T27" s="38" t="e">
         <f>E27*$T$2</f>
-        <v>0</v>
-      </c>
-      <c r="U27" s="51">
+        <v>#N/A</v>
+      </c>
+      <c r="U27" s="51" t="e">
         <f>F27*$T$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C28" s="21" t="s">
         <v>204</v>
       </c>
@@ -22244,7 +22180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C29" s="21" t="s">
         <v>177</v>
       </c>
@@ -22292,7 +22228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C30" s="21" t="s">
         <v>127</v>
       </c>
@@ -22345,7 +22281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C31" s="21" t="s">
         <v>128</v>
       </c>
@@ -22398,7 +22334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32"/>
       <c r="B32"/>
       <c r="C32" s="21" t="s">
@@ -22407,11 +22343,11 @@
       <c r="D32"/>
       <c r="E32" s="15">
         <f>'Calculations Retail'!C46*0.277776</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="15">
+        <v>17519.887872000003</v>
+      </c>
+      <c r="F32" s="15" t="e">
         <f>IF('Calculations Retail'!G42="Gas",'Calculations Retail'!G46*0.277776,'Calculations Retail'!G46)</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="G32" s="15"/>
       <c r="H32" s="15" t="str">
@@ -22421,11 +22357,11 @@
       <c r="I32" s="15"/>
       <c r="J32" s="15">
         <f>(E32*3.6*$J$3)/1000</f>
-        <v>0</v>
-      </c>
-      <c r="K32" s="15">
+        <v>3.2500793593589763</v>
+      </c>
+      <c r="K32" s="15" t="e">
         <f>IF('Calculations Retail'!G42="Gas",((F32*3.6*$J$3)/1000),((F32*$J$2)/1000))</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="L32" s="15"/>
       <c r="M32" s="15" t="str">
@@ -22435,11 +22371,11 @@
       <c r="N32" s="15"/>
       <c r="O32" s="15">
         <f>(E32*$J$3)/1000</f>
-        <v>0</v>
-      </c>
-      <c r="P32" s="15">
+        <v>0.90279982204416009</v>
+      </c>
+      <c r="P32" s="15" t="e">
         <f>IF('Calculations Retail'!G42="Gas",(J32),IF('Inputs Residential &amp; Mixed-Use'!D17="Whole Development",((F32*$J$4)/1000),((F32*$J$2)/1000)))</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="Q32"/>
       <c r="R32" t="str">
@@ -22449,25 +22385,25 @@
       <c r="S32"/>
       <c r="T32" s="52">
         <f>E32*3.6*$Y$2</f>
-        <v>0</v>
-      </c>
-      <c r="U32" s="53">
+        <v>2207.5058718720006</v>
+      </c>
+      <c r="U32" s="53" t="e">
         <f>IF('Calculations Retail'!G42="Gas",'Totals Residential &amp; Mixed-Use'!F32*3.6*'Totals Residential &amp; Mixed-Use'!Y2,'Totals Residential &amp; Mixed-Use'!F32*$T$2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C33" s="41" t="s">
         <v>120</v>
       </c>
       <c r="D33" s="45"/>
-      <c r="E33" s="42">
+      <c r="E33" s="42" t="e">
         <f>SUM(E27:E32)</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="42">
+        <v>#N/A</v>
+      </c>
+      <c r="F33" s="42" t="e">
         <f>SUM(F27:F32)</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="G33" s="42"/>
       <c r="H33" s="42" t="str">
@@ -22475,13 +22411,13 @@
         <v>Total</v>
       </c>
       <c r="I33" s="42"/>
-      <c r="J33" s="42">
+      <c r="J33" s="42" t="e">
         <f>SUM(J27:J32)</f>
-        <v>0</v>
-      </c>
-      <c r="K33" s="42">
+        <v>#N/A</v>
+      </c>
+      <c r="K33" s="42" t="e">
         <f>SUM(K27:K32)</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="L33" s="42"/>
       <c r="M33" s="42" t="str">
@@ -22489,13 +22425,13 @@
         <v>Total</v>
       </c>
       <c r="N33" s="42"/>
-      <c r="O33" s="42">
+      <c r="O33" s="42" t="e">
         <f>SUM(O27:O32)</f>
-        <v>0</v>
-      </c>
-      <c r="P33" s="42">
+        <v>#N/A</v>
+      </c>
+      <c r="P33" s="42" t="e">
         <f>SUM(P27:P32)</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="Q33" s="45"/>
       <c r="R33" s="45" t="str">
@@ -22503,16 +22439,16 @@
         <v>Total</v>
       </c>
       <c r="S33" s="45"/>
-      <c r="T33" s="46">
+      <c r="T33" s="46" t="e">
         <f>E33*$T$2</f>
-        <v>0</v>
-      </c>
-      <c r="U33" s="54">
+        <v>#N/A</v>
+      </c>
+      <c r="U33" s="54" t="e">
         <f>F33*$T$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E34" s="15"/>
       <c r="F34" s="15"/>
       <c r="G34" s="15"/>
@@ -22526,30 +22462,30 @@
       <c r="O34" s="15"/>
       <c r="P34" s="15"/>
     </row>
-    <row r="35" spans="3:21" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C35" s="137" t="s">
+    <row r="35" spans="3:21" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C35" s="139" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="138"/>
-      <c r="E35" s="138"/>
-      <c r="F35" s="138"/>
-      <c r="G35" s="138"/>
-      <c r="H35" s="138"/>
-      <c r="I35" s="138"/>
-      <c r="J35" s="138"/>
-      <c r="K35" s="138"/>
-      <c r="L35" s="138"/>
-      <c r="M35" s="138"/>
-      <c r="N35" s="138"/>
-      <c r="O35" s="138"/>
-      <c r="P35" s="138"/>
-      <c r="Q35" s="138"/>
-      <c r="R35" s="138"/>
-      <c r="S35" s="138"/>
-      <c r="T35" s="138"/>
-      <c r="U35" s="139"/>
-    </row>
-    <row r="36" spans="3:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="D35" s="140"/>
+      <c r="E35" s="140"/>
+      <c r="F35" s="140"/>
+      <c r="G35" s="140"/>
+      <c r="H35" s="140"/>
+      <c r="I35" s="140"/>
+      <c r="J35" s="140"/>
+      <c r="K35" s="140"/>
+      <c r="L35" s="140"/>
+      <c r="M35" s="140"/>
+      <c r="N35" s="140"/>
+      <c r="O35" s="140"/>
+      <c r="P35" s="140"/>
+      <c r="Q35" s="140"/>
+      <c r="R35" s="140"/>
+      <c r="S35" s="140"/>
+      <c r="T35" s="140"/>
+      <c r="U35" s="141"/>
+    </row>
+    <row r="36" spans="3:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C36" s="37" t="s">
         <v>138</v>
       </c>
@@ -22557,9 +22493,9 @@
       <c r="E36" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="F36" s="91" t="str">
+      <c r="F36" s="91">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
+        <v>0</v>
       </c>
       <c r="G36" s="8"/>
       <c r="H36" s="8" t="s">
@@ -22569,9 +22505,9 @@
       <c r="J36" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="K36" s="91" t="str">
+      <c r="K36" s="91">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
+        <v>0</v>
       </c>
       <c r="M36" s="91" t="s">
         <v>228</v>
@@ -22580,9 +22516,9 @@
       <c r="O36" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="P36" s="91" t="str">
+      <c r="P36" s="91">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
+        <v>0</v>
       </c>
       <c r="R36" s="8" t="s">
         <v>134</v>
@@ -22591,22 +22527,22 @@
       <c r="T36" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="U36" s="98" t="str">
+      <c r="U36" s="98">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
-      </c>
-    </row>
-    <row r="37" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C37" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="E37" s="15">
+      <c r="E37" s="15" t="e">
         <f>'Calculations Office'!C9</f>
-        <v>0</v>
-      </c>
-      <c r="F37" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="F37" s="15" t="e">
         <f>'Calculations Office'!G9</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="G37" s="15"/>
       <c r="H37" s="15" t="str">
@@ -22614,13 +22550,13 @@
         <v>Heating &amp; Cooling (Elec)</v>
       </c>
       <c r="I37" s="15"/>
-      <c r="J37" s="15">
+      <c r="J37" s="15" t="e">
         <f>(E37*$J$2)/1000</f>
-        <v>0</v>
-      </c>
-      <c r="K37" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="K37" s="15" t="e">
         <f>(F37*$J$2)/1000</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="L37" s="15"/>
       <c r="M37" s="15" t="str">
@@ -22628,28 +22564,28 @@
         <v>Heating &amp; Cooling (Elec)</v>
       </c>
       <c r="N37" s="15"/>
-      <c r="O37" s="15">
+      <c r="O37" s="15" t="e">
         <f t="shared" ref="O37:O42" si="10">(E37*$J$2)/1000</f>
-        <v>0</v>
-      </c>
-      <c r="P37" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="P37" s="15" t="e">
         <f>IF('Inputs Residential &amp; Mixed-Use'!$D$17="Whole Development",((F37*$J$4)/1000),((F37*$J$2)/1000))</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="R37" t="str">
         <f>C37</f>
         <v>Heating &amp; Cooling (Elec)</v>
       </c>
-      <c r="T37" s="38">
+      <c r="T37" s="38" t="e">
         <f>E37*$T$2</f>
-        <v>0</v>
-      </c>
-      <c r="U37" s="51">
+        <v>#N/A</v>
+      </c>
+      <c r="U37" s="51" t="e">
         <f>F37*$T$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="3:21" x14ac:dyDescent="0.25">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="38" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C38" s="21" t="s">
         <v>204</v>
       </c>
@@ -22702,7 +22638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C39" s="21" t="s">
         <v>177</v>
       </c>
@@ -22750,7 +22686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C40" s="21" t="s">
         <v>126</v>
       </c>
@@ -22803,7 +22739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C41" s="21" t="s">
         <v>127</v>
       </c>
@@ -22856,7 +22792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C42" s="21" t="s">
         <v>128</v>
       </c>
@@ -22909,18 +22845,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C43" s="41" t="s">
         <v>120</v>
       </c>
       <c r="D43" s="45"/>
-      <c r="E43" s="42">
+      <c r="E43" s="42" t="e">
         <f>SUM(E37:E42)</f>
-        <v>0</v>
-      </c>
-      <c r="F43" s="42">
+        <v>#N/A</v>
+      </c>
+      <c r="F43" s="42" t="e">
         <f>SUM(F37:F42)</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="G43" s="42"/>
       <c r="H43" s="42" t="str">
@@ -22928,13 +22864,13 @@
         <v>Total</v>
       </c>
       <c r="I43" s="42"/>
-      <c r="J43" s="42">
+      <c r="J43" s="42" t="e">
         <f>SUM(J37:J42)</f>
-        <v>0</v>
-      </c>
-      <c r="K43" s="42">
+        <v>#N/A</v>
+      </c>
+      <c r="K43" s="42" t="e">
         <f>SUM(K37:K42)</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="L43" s="42"/>
       <c r="M43" s="42" t="str">
@@ -22942,13 +22878,13 @@
         <v>Total</v>
       </c>
       <c r="N43" s="42"/>
-      <c r="O43" s="42">
+      <c r="O43" s="42" t="e">
         <f>SUM(O37:O42)</f>
-        <v>0</v>
-      </c>
-      <c r="P43" s="42">
+        <v>#N/A</v>
+      </c>
+      <c r="P43" s="42" t="e">
         <f>SUM(P37:P42)</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="Q43" s="45"/>
       <c r="R43" s="45" t="str">
@@ -22956,16 +22892,16 @@
         <v>Total</v>
       </c>
       <c r="S43" s="45"/>
-      <c r="T43" s="46">
+      <c r="T43" s="46" t="e">
         <f>E43</f>
-        <v>0</v>
-      </c>
-      <c r="U43" s="54">
+        <v>#N/A</v>
+      </c>
+      <c r="U43" s="54" t="e">
         <f>F43</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="44" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="18"/>
@@ -22986,30 +22922,30 @@
       <c r="T44" s="19"/>
       <c r="U44" s="19"/>
     </row>
-    <row r="45" spans="3:21" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C45" s="137" t="s">
+    <row r="45" spans="3:21" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C45" s="139" t="s">
         <v>173</v>
       </c>
-      <c r="D45" s="138"/>
-      <c r="E45" s="138"/>
-      <c r="F45" s="138"/>
-      <c r="G45" s="138"/>
-      <c r="H45" s="138"/>
-      <c r="I45" s="138"/>
-      <c r="J45" s="138"/>
-      <c r="K45" s="138"/>
-      <c r="L45" s="138"/>
-      <c r="M45" s="138"/>
-      <c r="N45" s="138"/>
-      <c r="O45" s="138"/>
-      <c r="P45" s="138"/>
-      <c r="Q45" s="138"/>
-      <c r="R45" s="138"/>
-      <c r="S45" s="138"/>
-      <c r="T45" s="138"/>
-      <c r="U45" s="139"/>
-    </row>
-    <row r="46" spans="3:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="D45" s="140"/>
+      <c r="E45" s="140"/>
+      <c r="F45" s="140"/>
+      <c r="G45" s="140"/>
+      <c r="H45" s="140"/>
+      <c r="I45" s="140"/>
+      <c r="J45" s="140"/>
+      <c r="K45" s="140"/>
+      <c r="L45" s="140"/>
+      <c r="M45" s="140"/>
+      <c r="N45" s="140"/>
+      <c r="O45" s="140"/>
+      <c r="P45" s="140"/>
+      <c r="Q45" s="140"/>
+      <c r="R45" s="140"/>
+      <c r="S45" s="140"/>
+      <c r="T45" s="140"/>
+      <c r="U45" s="141"/>
+    </row>
+    <row r="46" spans="3:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C46" s="37" t="s">
         <v>138</v>
       </c>
@@ -23017,9 +22953,9 @@
       <c r="E46" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="F46" s="91" t="str">
+      <c r="F46" s="91">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
+        <v>0</v>
       </c>
       <c r="G46" s="8"/>
       <c r="H46" s="8" t="s">
@@ -23029,9 +22965,9 @@
       <c r="J46" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="K46" s="8" t="str">
+      <c r="K46" s="8">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
+        <v>0</v>
       </c>
       <c r="M46" s="91" t="s">
         <v>228</v>
@@ -23040,9 +22976,9 @@
       <c r="O46" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="P46" s="91" t="str">
+      <c r="P46" s="91">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
+        <v>0</v>
       </c>
       <c r="R46" s="8" t="s">
         <v>134</v>
@@ -23051,22 +22987,22 @@
       <c r="T46" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="U46" s="98" t="str">
+      <c r="U46" s="98">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
-      </c>
-    </row>
-    <row r="47" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C47" s="21" t="s">
         <v>174</v>
       </c>
       <c r="E47" s="15">
         <f>'Calculations C&amp;S'!C4</f>
-        <v>5051.1542399999989</v>
+        <v>0</v>
       </c>
       <c r="F47" s="15">
         <f>'Calculations C&amp;S'!G4</f>
-        <v>5051.1542399999989</v>
+        <v>0</v>
       </c>
       <c r="G47" s="15"/>
       <c r="H47" t="s">
@@ -23074,11 +23010,11 @@
       </c>
       <c r="J47" s="15">
         <f>(E47*$J$2)/1000</f>
-        <v>4.3439926463999994</v>
+        <v>0</v>
       </c>
       <c r="K47" s="15">
         <f>(F47*$J$2)/1000</f>
-        <v>4.3439926463999994</v>
+        <v>0</v>
       </c>
       <c r="L47" s="15"/>
       <c r="M47" t="s">
@@ -23086,35 +23022,35 @@
       </c>
       <c r="O47" s="15">
         <f>(E47*$J$2)/1000</f>
-        <v>4.3439926463999994</v>
+        <v>0</v>
       </c>
       <c r="P47" s="15">
         <f>IF('Inputs Residential &amp; Mixed-Use'!$D$17="Whole Development",F47*$J$4/1000, IF('Inputs Residential &amp; Mixed-Use'!$D$17="Base Building",F47*$J$4/1000,F47*$J$2/1000))</f>
-        <v>4.3439926463999994</v>
+        <v>0</v>
       </c>
       <c r="R47" t="s">
         <v>174</v>
       </c>
       <c r="T47" s="52">
         <f>E47*$T$2</f>
-        <v>1459.7835753599995</v>
+        <v>0</v>
       </c>
       <c r="U47" s="53">
         <f>F47*$T$2</f>
-        <v>1459.7835753599995</v>
-      </c>
-    </row>
-    <row r="48" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C48" s="21" t="s">
         <v>127</v>
       </c>
       <c r="E48" s="15">
         <f>'Calculations C&amp;S'!C10+'Calculations C&amp;S'!C16</f>
-        <v>2375.712</v>
+        <v>0</v>
       </c>
       <c r="F48" s="15">
         <f>'Calculations C&amp;S'!G10+'Calculations C&amp;S'!G16</f>
-        <v>2375.712</v>
+        <v>0</v>
       </c>
       <c r="G48" s="15"/>
       <c r="H48" t="s">
@@ -23122,11 +23058,11 @@
       </c>
       <c r="J48" s="15">
         <f>(E48*$J$2)/1000</f>
-        <v>2.0431123200000001</v>
+        <v>0</v>
       </c>
       <c r="K48" s="15">
         <f>(F48*$J$2)/1000</f>
-        <v>2.0431123200000001</v>
+        <v>0</v>
       </c>
       <c r="L48" s="15"/>
       <c r="M48" t="s">
@@ -23134,36 +23070,36 @@
       </c>
       <c r="O48" s="15">
         <f>(E48*$J$2)/1000</f>
-        <v>2.0431123200000001</v>
+        <v>0</v>
       </c>
       <c r="P48" s="15">
         <f>IF('Inputs Residential &amp; Mixed-Use'!$D$17="Whole Development",F48*$J$4/1000, IF('Inputs Residential &amp; Mixed-Use'!$D$17="Base Building",F48*$J$4/1000,F48*$J$2/1000))</f>
-        <v>2.0431123200000001</v>
+        <v>0</v>
       </c>
       <c r="R48" t="s">
         <v>127</v>
       </c>
       <c r="T48" s="52">
         <f>E48*$T$2</f>
-        <v>686.58076799999992</v>
+        <v>0</v>
       </c>
       <c r="U48" s="53">
         <f>F48*$T$2</f>
-        <v>686.58076799999992</v>
-      </c>
-    </row>
-    <row r="49" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C49" s="41" t="s">
         <v>120</v>
       </c>
       <c r="D49" s="45"/>
       <c r="E49" s="42">
         <f>SUM(E47:E48)</f>
-        <v>7426.8662399999994</v>
+        <v>0</v>
       </c>
       <c r="F49" s="42">
         <f>SUM(F47:F48)</f>
-        <v>7426.8662399999994</v>
+        <v>0</v>
       </c>
       <c r="G49" s="42"/>
       <c r="H49" s="45" t="s">
@@ -23172,11 +23108,11 @@
       <c r="I49" s="45"/>
       <c r="J49" s="42">
         <f>SUM(J47:J48)</f>
-        <v>6.387104966399999</v>
+        <v>0</v>
       </c>
       <c r="K49" s="42">
         <f>SUM(K47:K48)</f>
-        <v>6.387104966399999</v>
+        <v>0</v>
       </c>
       <c r="L49" s="42"/>
       <c r="M49" s="45" t="s">
@@ -23185,11 +23121,11 @@
       <c r="N49" s="45"/>
       <c r="O49" s="42">
         <f>SUM(O47:O48)</f>
-        <v>6.387104966399999</v>
+        <v>0</v>
       </c>
       <c r="P49" s="42">
         <f>SUM(P47:P48)</f>
-        <v>6.387104966399999</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="45"/>
       <c r="R49" s="45" t="s">
@@ -23198,14 +23134,14 @@
       <c r="S49" s="45"/>
       <c r="T49" s="46">
         <f>SUM(T47:T48)</f>
-        <v>2146.3643433599996</v>
+        <v>0</v>
       </c>
       <c r="U49" s="54">
         <f>SUM(U47:U48)</f>
-        <v>2146.3643433599996</v>
-      </c>
-    </row>
-    <row r="50" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E50" s="15"/>
       <c r="F50" s="15"/>
       <c r="G50" s="15"/>
@@ -23219,30 +23155,30 @@
       <c r="O50" s="15"/>
       <c r="P50" s="15"/>
     </row>
-    <row r="51" spans="3:21" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C51" s="137" t="s">
+    <row r="51" spans="3:21" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C51" s="139" t="s">
         <v>129</v>
       </c>
-      <c r="D51" s="138"/>
-      <c r="E51" s="138"/>
-      <c r="F51" s="138"/>
-      <c r="G51" s="138"/>
-      <c r="H51" s="138"/>
-      <c r="I51" s="138"/>
-      <c r="J51" s="138"/>
-      <c r="K51" s="138"/>
-      <c r="L51" s="138"/>
-      <c r="M51" s="138"/>
-      <c r="N51" s="138"/>
-      <c r="O51" s="138"/>
-      <c r="P51" s="138"/>
-      <c r="Q51" s="138"/>
-      <c r="R51" s="138"/>
-      <c r="S51" s="138"/>
-      <c r="T51" s="138"/>
-      <c r="U51" s="139"/>
-    </row>
-    <row r="52" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D51" s="140"/>
+      <c r="E51" s="140"/>
+      <c r="F51" s="140"/>
+      <c r="G51" s="140"/>
+      <c r="H51" s="140"/>
+      <c r="I51" s="140"/>
+      <c r="J51" s="140"/>
+      <c r="K51" s="140"/>
+      <c r="L51" s="140"/>
+      <c r="M51" s="140"/>
+      <c r="N51" s="140"/>
+      <c r="O51" s="140"/>
+      <c r="P51" s="140"/>
+      <c r="Q51" s="140"/>
+      <c r="R51" s="140"/>
+      <c r="S51" s="140"/>
+      <c r="T51" s="140"/>
+      <c r="U51" s="141"/>
+    </row>
+    <row r="52" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C52" s="22" t="s">
         <v>139</v>
       </c>
@@ -23252,11 +23188,11 @@
       </c>
       <c r="F52" s="43">
         <f>IF('Inputs Residential &amp; Mixed-Use'!D40=0,('Inputs Residential &amp; Mixed-Use'!D41*'Inputs Residential &amp; Mixed-Use'!D6*-1),('Inputs Residential &amp; Mixed-Use'!D40*-1))</f>
-        <v>-12200</v>
+        <v>0</v>
       </c>
       <c r="G52" s="43"/>
       <c r="H52" s="43" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I52" s="43"/>
       <c r="J52" s="43">
@@ -23265,7 +23201,7 @@
       </c>
       <c r="K52" s="43">
         <f>(F52*$J$2)/1000</f>
-        <v>-10.492000000000001</v>
+        <v>0</v>
       </c>
       <c r="L52" s="43"/>
       <c r="M52" s="43" t="str">
@@ -23279,7 +23215,7 @@
       </c>
       <c r="P52" s="43">
         <f>(F52*$J$2)/1000</f>
-        <v>-10.492000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="44"/>
       <c r="R52" s="44" t="str">
@@ -23293,10 +23229,10 @@
       </c>
       <c r="U52" s="55">
         <f>F52*$T$2</f>
-        <v>-3525.7999999999997</v>
-      </c>
-    </row>
-    <row r="53" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E53" s="15"/>
       <c r="F53" s="15"/>
       <c r="G53" s="15"/>
@@ -23310,30 +23246,30 @@
       <c r="O53" s="15"/>
       <c r="P53" s="15"/>
     </row>
-    <row r="54" spans="3:21" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C54" s="137" t="s">
+    <row r="54" spans="3:21" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C54" s="139" t="s">
         <v>137</v>
       </c>
-      <c r="D54" s="138"/>
-      <c r="E54" s="138"/>
-      <c r="F54" s="138"/>
-      <c r="G54" s="138"/>
-      <c r="H54" s="138"/>
-      <c r="I54" s="138"/>
-      <c r="J54" s="138"/>
-      <c r="K54" s="138"/>
-      <c r="L54" s="138"/>
-      <c r="M54" s="138"/>
-      <c r="N54" s="138"/>
-      <c r="O54" s="138"/>
-      <c r="P54" s="138"/>
-      <c r="Q54" s="138"/>
-      <c r="R54" s="138"/>
-      <c r="S54" s="138"/>
-      <c r="T54" s="138"/>
-      <c r="U54" s="139"/>
-    </row>
-    <row r="55" spans="3:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="D54" s="140"/>
+      <c r="E54" s="140"/>
+      <c r="F54" s="140"/>
+      <c r="G54" s="140"/>
+      <c r="H54" s="140"/>
+      <c r="I54" s="140"/>
+      <c r="J54" s="140"/>
+      <c r="K54" s="140"/>
+      <c r="L54" s="140"/>
+      <c r="M54" s="140"/>
+      <c r="N54" s="140"/>
+      <c r="O54" s="140"/>
+      <c r="P54" s="140"/>
+      <c r="Q54" s="140"/>
+      <c r="R54" s="140"/>
+      <c r="S54" s="140"/>
+      <c r="T54" s="140"/>
+      <c r="U54" s="141"/>
+    </row>
+    <row r="55" spans="3:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C55" s="37" t="s">
         <v>138</v>
       </c>
@@ -23343,9 +23279,9 @@
       <c r="E55" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="F55" s="91" t="str">
+      <c r="F55" s="91">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
+        <v>0</v>
       </c>
       <c r="G55" s="8"/>
       <c r="H55" s="8" t="s">
@@ -23357,9 +23293,9 @@
       <c r="J55" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="K55" s="91" t="str">
+      <c r="K55" s="91">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
+        <v>0</v>
       </c>
       <c r="M55" s="91" t="s">
         <v>228</v>
@@ -23382,293 +23318,293 @@
       <c r="T55" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="U55" s="98" t="str">
+      <c r="U55" s="98">
         <f>'Inputs Residential &amp; Mixed-Use'!D5</f>
-        <v>Address</v>
-      </c>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C56" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D56" s="15">
+      <c r="D56" s="15" t="e">
         <f>D15</f>
-        <v>156092.33532094717</v>
-      </c>
-      <c r="E56" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="E56" s="15" t="e">
         <f>E15</f>
-        <v>87885.172379435156</v>
-      </c>
-      <c r="F56" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="F56" s="15" t="e">
         <f>F15</f>
-        <v>63885.067546663922</v>
+        <v>#N/A</v>
       </c>
       <c r="G56" s="15"/>
       <c r="H56" s="15" t="str">
         <f t="shared" ref="H56:H62" si="13">C56</f>
         <v>Residential</v>
       </c>
-      <c r="I56" s="15">
+      <c r="I56" s="15" t="e">
         <f>I15</f>
-        <v>64.62353456273334</v>
-      </c>
-      <c r="J56" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="J56" s="15" t="e">
         <f>J15</f>
-        <v>75.581248246314232</v>
-      </c>
-      <c r="K56" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="K56" s="15" t="e">
         <f>K15</f>
-        <v>54.941158090130976</v>
+        <v>#N/A</v>
       </c>
       <c r="L56" s="15"/>
       <c r="M56" s="15" t="str">
         <f>H56</f>
         <v>Residential</v>
       </c>
-      <c r="N56" s="15">
+      <c r="N56" s="15" t="e">
         <f>N15</f>
-        <v>64.62353456273334</v>
-      </c>
-      <c r="O56" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="O56" s="15" t="e">
         <f>O15</f>
-        <v>75.581248246314232</v>
-      </c>
-      <c r="P56" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="P56" s="15" t="e">
         <f>P15</f>
-        <v>54.941158090130976</v>
+        <v>#N/A</v>
       </c>
       <c r="Q56" s="15"/>
       <c r="R56" t="s">
         <v>16</v>
       </c>
-      <c r="S56" s="15">
+      <c r="S56" s="15" t="e">
         <f>S15</f>
-        <v>28287.079243691234</v>
-      </c>
-      <c r="T56" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="T56" s="15" t="e">
         <f>T15</f>
-        <v>25398.814817656756</v>
-      </c>
-      <c r="U56" s="49">
+        <v>#N/A</v>
+      </c>
+      <c r="U56" s="49" t="e">
         <f>U15</f>
-        <v>18462.784520985875</v>
-      </c>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.25">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C57" s="21" t="s">
         <v>169</v>
       </c>
       <c r="D57" s="15">
         <f>E57</f>
-        <v>24344.080888888886</v>
+        <v>0</v>
       </c>
       <c r="E57" s="15">
         <f>E23</f>
-        <v>24344.080888888886</v>
+        <v>0</v>
       </c>
       <c r="F57" s="15">
         <f>F23</f>
-        <v>24344.080888888886</v>
+        <v>0</v>
       </c>
       <c r="G57" s="15"/>
       <c r="H57" s="15" t="str">
         <f t="shared" si="13"/>
         <v>Communal</v>
       </c>
-      <c r="I57" s="15">
+      <c r="I57" s="15" t="e">
         <f>J57</f>
-        <v>21.531251499928317</v>
-      </c>
-      <c r="J57" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="J57" s="15" t="e">
         <f>J23</f>
-        <v>21.531251499928317</v>
-      </c>
-      <c r="K57" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="K57" s="15" t="e">
         <f>K23</f>
-        <v>21.531251499928317</v>
+        <v>#N/A</v>
       </c>
       <c r="L57" s="15"/>
       <c r="M57" t="s">
         <v>169</v>
       </c>
-      <c r="N57" s="15">
+      <c r="N57" s="15" t="e">
         <f>O57</f>
-        <v>21.531251499928317</v>
-      </c>
-      <c r="O57" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="O57" s="15" t="e">
         <f>O23</f>
-        <v>21.531251499928317</v>
-      </c>
-      <c r="P57" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="P57" s="15" t="e">
         <f>P23</f>
-        <v>21.531251499928317</v>
+        <v>#N/A</v>
       </c>
       <c r="Q57" s="15"/>
       <c r="R57" t="s">
         <v>169</v>
       </c>
-      <c r="S57" s="15">
+      <c r="S57" s="15" t="e">
         <f>T57</f>
-        <v>7235.5019575340493</v>
-      </c>
-      <c r="T57" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="T57" s="15" t="e">
         <f>T23</f>
-        <v>7235.5019575340493</v>
-      </c>
-      <c r="U57" s="49">
+        <v>#N/A</v>
+      </c>
+      <c r="U57" s="49" t="e">
         <f>U23</f>
-        <v>7235.5019575340493</v>
-      </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.25">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C58" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D58" s="15">
+      <c r="D58" s="15" t="e">
         <f>E58</f>
-        <v>0</v>
-      </c>
-      <c r="E58" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="E58" s="15" t="e">
         <f>E33</f>
-        <v>0</v>
-      </c>
-      <c r="F58" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="F58" s="15" t="e">
         <f>F33</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="G58" s="15"/>
       <c r="H58" s="15" t="str">
         <f t="shared" si="13"/>
         <v>Retail</v>
       </c>
-      <c r="I58" s="15">
+      <c r="I58" s="15" t="e">
         <f>J58</f>
-        <v>0</v>
-      </c>
-      <c r="J58" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="J58" s="15" t="e">
         <f>J33</f>
-        <v>0</v>
-      </c>
-      <c r="K58" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="K58" s="15" t="e">
         <f>K33</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="L58" s="15"/>
       <c r="M58" s="15" t="str">
         <f>H58</f>
         <v>Retail</v>
       </c>
-      <c r="N58" s="15">
+      <c r="N58" s="15" t="e">
         <f>O58</f>
-        <v>0</v>
-      </c>
-      <c r="O58" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="O58" s="15" t="e">
         <f>O33</f>
-        <v>0</v>
-      </c>
-      <c r="P58" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="P58" s="15" t="e">
         <f>P33</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="Q58" s="15"/>
       <c r="R58" t="s">
         <v>1</v>
       </c>
-      <c r="S58" s="15">
+      <c r="S58" s="15" t="e">
         <f>T58</f>
-        <v>0</v>
-      </c>
-      <c r="T58" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="T58" s="15" t="e">
         <f>T33</f>
-        <v>0</v>
-      </c>
-      <c r="U58" s="49">
+        <v>#N/A</v>
+      </c>
+      <c r="U58" s="49" t="e">
         <f>U33</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.25">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C59" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D59" s="15">
+      <c r="D59" s="15" t="e">
         <f>E59</f>
-        <v>0</v>
-      </c>
-      <c r="E59" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="E59" s="15" t="e">
         <f>E43</f>
-        <v>0</v>
-      </c>
-      <c r="F59" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="F59" s="15" t="e">
         <f>F43</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="G59" s="15"/>
       <c r="H59" s="15" t="str">
         <f t="shared" si="13"/>
         <v>Office</v>
       </c>
-      <c r="I59" s="15">
+      <c r="I59" s="15" t="e">
         <f>J59</f>
-        <v>0</v>
-      </c>
-      <c r="J59" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="J59" s="15" t="e">
         <f>J43</f>
-        <v>0</v>
-      </c>
-      <c r="K59" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="K59" s="15" t="e">
         <f>K43</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="L59" s="15"/>
       <c r="M59" s="15" t="str">
         <f>H59</f>
         <v>Office</v>
       </c>
-      <c r="N59" s="15">
+      <c r="N59" s="15" t="e">
         <f>O59</f>
-        <v>0</v>
-      </c>
-      <c r="O59" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="O59" s="15" t="e">
         <f>O43</f>
-        <v>0</v>
-      </c>
-      <c r="P59" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="P59" s="15" t="e">
         <f>P43</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="Q59" s="15"/>
       <c r="R59" t="s">
         <v>2</v>
       </c>
-      <c r="S59" s="15">
+      <c r="S59" s="15" t="e">
         <f>T59</f>
-        <v>0</v>
-      </c>
-      <c r="T59" s="15">
+        <v>#N/A</v>
+      </c>
+      <c r="T59" s="15" t="e">
         <f>T43</f>
-        <v>0</v>
-      </c>
-      <c r="U59" s="49">
+        <v>#N/A</v>
+      </c>
+      <c r="U59" s="49" t="e">
         <f>U43</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.25">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C60" s="21" t="s">
         <v>173</v>
       </c>
       <c r="D60" s="15">
         <f>E60</f>
-        <v>7426.8662399999994</v>
+        <v>0</v>
       </c>
       <c r="E60" s="15">
         <f>E49</f>
-        <v>7426.8662399999994</v>
+        <v>0</v>
       </c>
       <c r="F60" s="15">
         <f>F49</f>
-        <v>7426.8662399999994</v>
+        <v>0</v>
       </c>
       <c r="G60" s="15"/>
       <c r="H60" s="15" t="str">
@@ -23677,15 +23613,15 @@
       </c>
       <c r="I60" s="15">
         <f>J60</f>
-        <v>6.387104966399999</v>
+        <v>0</v>
       </c>
       <c r="J60" s="15">
         <f>J49</f>
-        <v>6.387104966399999</v>
+        <v>0</v>
       </c>
       <c r="K60" s="15">
         <f>K49</f>
-        <v>6.387104966399999</v>
+        <v>0</v>
       </c>
       <c r="L60" s="15"/>
       <c r="M60" t="s">
@@ -23693,15 +23629,15 @@
       </c>
       <c r="N60" s="15">
         <f>O60</f>
-        <v>6.387104966399999</v>
+        <v>0</v>
       </c>
       <c r="O60" s="15">
         <f>O49</f>
-        <v>6.387104966399999</v>
+        <v>0</v>
       </c>
       <c r="P60" s="15">
         <f>P49</f>
-        <v>6.387104966399999</v>
+        <v>0</v>
       </c>
       <c r="Q60" s="15"/>
       <c r="R60" t="s">
@@ -23709,18 +23645,18 @@
       </c>
       <c r="S60" s="15">
         <f>T60</f>
-        <v>2146.3643433599996</v>
+        <v>0</v>
       </c>
       <c r="T60" s="15">
         <f>T49</f>
-        <v>2146.3643433599996</v>
+        <v>0</v>
       </c>
       <c r="U60" s="49">
         <f>U49</f>
-        <v>2146.3643433599996</v>
-      </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C61" s="21" t="s">
         <v>129</v>
       </c>
@@ -23734,7 +23670,7 @@
       </c>
       <c r="F61" s="15">
         <f>F52</f>
-        <v>-12200</v>
+        <v>0</v>
       </c>
       <c r="G61" s="15"/>
       <c r="H61" s="15" t="str">
@@ -23751,7 +23687,7 @@
       </c>
       <c r="K61" s="15">
         <f>K52</f>
-        <v>-10.492000000000001</v>
+        <v>0</v>
       </c>
       <c r="L61" s="15"/>
       <c r="M61" s="15" t="str">
@@ -23768,7 +23704,7 @@
       </c>
       <c r="P61" s="15">
         <f>P52</f>
-        <v>-10.492000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="15"/>
       <c r="R61" t="s">
@@ -23784,80 +23720,80 @@
       </c>
       <c r="U61" s="49">
         <f>U52</f>
-        <v>-3525.7999999999997</v>
-      </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C62" s="80" t="s">
         <v>120</v>
       </c>
-      <c r="D62" s="18">
+      <c r="D62" s="18" t="e">
         <f>SUM(D56:D61)</f>
-        <v>187863.28244983606</v>
-      </c>
-      <c r="E62" s="18">
+        <v>#N/A</v>
+      </c>
+      <c r="E62" s="18" t="e">
         <f>SUM(E56:E61)</f>
-        <v>119656.11950832405</v>
-      </c>
-      <c r="F62" s="18">
+        <v>#N/A</v>
+      </c>
+      <c r="F62" s="18" t="e">
         <f>SUM(F56:F61)</f>
-        <v>83456.014675552811</v>
+        <v>#N/A</v>
       </c>
       <c r="G62" s="18"/>
       <c r="H62" s="18" t="str">
         <f t="shared" si="13"/>
         <v>Total</v>
       </c>
-      <c r="I62" s="18">
+      <c r="I62" s="18" t="e">
         <f>SUM(I56:I61)</f>
-        <v>92.541891029061659</v>
-      </c>
-      <c r="J62" s="18">
+        <v>#N/A</v>
+      </c>
+      <c r="J62" s="18" t="e">
         <f>SUM(J56:J61)</f>
-        <v>103.49960471264255</v>
-      </c>
-      <c r="K62" s="18">
+        <v>#N/A</v>
+      </c>
+      <c r="K62" s="18" t="e">
         <f>SUM(K56:K61)</f>
-        <v>72.367514556459298</v>
-      </c>
-      <c r="L62" s="18">
+        <v>#N/A</v>
+      </c>
+      <c r="L62" s="18" t="e">
         <f>K62-J62</f>
-        <v>-31.132090156183253</v>
+        <v>#N/A</v>
       </c>
       <c r="M62" s="18" t="str">
         <f>H62</f>
         <v>Total</v>
       </c>
-      <c r="N62" s="18">
+      <c r="N62" s="18" t="e">
         <f>SUM(N56:N61)</f>
-        <v>92.541891029061659</v>
-      </c>
-      <c r="O62" s="18">
+        <v>#N/A</v>
+      </c>
+      <c r="O62" s="18" t="e">
         <f>SUM(O56:O61)</f>
-        <v>103.49960471264255</v>
-      </c>
-      <c r="P62" s="18">
+        <v>#N/A</v>
+      </c>
+      <c r="P62" s="18" t="e">
         <f>SUM(P56:P61)</f>
-        <v>72.367514556459298</v>
+        <v>#N/A</v>
       </c>
       <c r="Q62" s="18"/>
       <c r="R62" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="S62" s="18">
+      <c r="S62" s="18" t="e">
         <f>SUM(S56:S61)</f>
-        <v>37668.945544585287</v>
-      </c>
-      <c r="T62" s="18">
+        <v>#N/A</v>
+      </c>
+      <c r="T62" s="18" t="e">
         <f>SUM(T56:T61)</f>
-        <v>34780.681118550805</v>
-      </c>
-      <c r="U62" s="81">
+        <v>#N/A</v>
+      </c>
+      <c r="U62" s="81" t="e">
         <f>SUM(U56:U61)</f>
-        <v>24318.850821879925</v>
-      </c>
-    </row>
-    <row r="63" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C63" s="41"/>
       <c r="D63" s="78"/>
       <c r="E63" s="78"/>
@@ -23868,9 +23804,9 @@
       </c>
       <c r="I63" s="78"/>
       <c r="J63" s="78"/>
-      <c r="K63" s="78">
+      <c r="K63" s="78" t="e">
         <f>1-(K62/J62)</f>
-        <v>0.30079429039964678</v>
+        <v>#N/A</v>
       </c>
       <c r="L63" s="42"/>
       <c r="M63" s="42"/>
@@ -23881,17 +23817,17 @@
       <c r="R63" s="42" t="s">
         <v>241</v>
       </c>
-      <c r="S63" s="99">
+      <c r="S63" s="99" t="e">
         <f>S62-U62</f>
-        <v>13350.094722705362</v>
-      </c>
-      <c r="T63" s="99">
+        <v>#N/A</v>
+      </c>
+      <c r="T63" s="99" t="e">
         <f>T62-U62</f>
-        <v>10461.83029667088</v>
+        <v>#N/A</v>
       </c>
       <c r="U63" s="79"/>
     </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="18"/>
@@ -23911,33 +23847,33 @@
       <c r="T64" s="18"/>
       <c r="U64" s="18"/>
     </row>
-    <row r="65" spans="3:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="66" spans="3:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C66" s="137" t="s">
+    <row r="65" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="66" spans="3:16" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C66" s="139" t="s">
         <v>221</v>
       </c>
-      <c r="D66" s="138"/>
-      <c r="E66" s="138"/>
-      <c r="F66" s="138"/>
-      <c r="G66" s="138"/>
-      <c r="H66" s="138"/>
-      <c r="I66" s="138"/>
-      <c r="J66" s="138"/>
-      <c r="K66" s="139"/>
+      <c r="D66" s="140"/>
+      <c r="E66" s="140"/>
+      <c r="F66" s="140"/>
+      <c r="G66" s="140"/>
+      <c r="H66" s="140"/>
+      <c r="I66" s="140"/>
+      <c r="J66" s="140"/>
+      <c r="K66" s="141"/>
       <c r="L66" s="106"/>
       <c r="M66" s="106"/>
       <c r="N66" s="106"/>
       <c r="O66" s="106"/>
       <c r="P66" s="106"/>
     </row>
-    <row r="67" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C67" s="21" t="str">
         <f>'Inputs Residential &amp; Mixed-Use'!P51</f>
         <v>Reference Potable Water Use (BESS)</v>
       </c>
       <c r="E67">
         <f>'Inputs Residential &amp; Mixed-Use'!Q51</f>
-        <v>978</v>
+        <v>0</v>
       </c>
       <c r="F67" t="s">
         <v>218</v>
@@ -23947,13 +23883,13 @@
       </c>
       <c r="J67">
         <f>E67</f>
-        <v>978</v>
+        <v>0</v>
       </c>
       <c r="K67" s="57" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="68" spans="3:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C68" s="76" t="str">
         <f>'Inputs Residential &amp; Mixed-Use'!P52</f>
         <v>Proposed (excluding rainwater and recycled water use) (BESS)</v>
@@ -23961,27 +23897,27 @@
       <c r="D68" s="82"/>
       <c r="E68">
         <f>'Inputs Residential &amp; Mixed-Use'!Q52</f>
-        <v>790</v>
+        <v>0</v>
       </c>
       <c r="F68" t="s">
         <v>218</v>
       </c>
-      <c r="G68" s="83">
+      <c r="G68" s="83" t="e">
         <f>1-(E68/E67)</f>
-        <v>0.19222903885480569</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H68" t="s">
         <v>223</v>
       </c>
       <c r="J68">
         <f>E68-E67</f>
-        <v>-188</v>
+        <v>0</v>
       </c>
       <c r="K68" s="57" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="3:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:16" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C69" s="77" t="str">
         <f>'Inputs Residential &amp; Mixed-Use'!P53</f>
         <v>Proposed (including rainwater and recycled water use) (BESS)</v>
@@ -23989,14 +23925,14 @@
       <c r="D69" s="93"/>
       <c r="E69" s="44">
         <f>'Inputs Residential &amp; Mixed-Use'!Q53</f>
-        <v>665</v>
+        <v>0</v>
       </c>
       <c r="F69" s="44" t="s">
         <v>218</v>
       </c>
-      <c r="G69" s="84">
+      <c r="G69" s="84" t="e">
         <f>(1-(E69/E67))</f>
-        <v>0.32004089979550099</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H69" s="44" t="s">
         <v>222</v>
@@ -24004,14 +23940,14 @@
       <c r="I69" s="44"/>
       <c r="J69" s="44">
         <f>E69-E68</f>
-        <v>-125</v>
+        <v>0</v>
       </c>
       <c r="K69" s="75" t="s">
         <v>218</v>
       </c>
       <c r="O69" s="15"/>
     </row>
-    <row r="70" spans="3:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C70" s="82"/>
       <c r="D70" s="82"/>
       <c r="G70" t="s">
@@ -24020,11 +23956,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="R3:S3"/>
     <mergeCell ref="C6:Z6"/>
     <mergeCell ref="C25:U25"/>
     <mergeCell ref="C35:U35"/>
@@ -24033,6 +23964,11 @@
     <mergeCell ref="C54:U54"/>
     <mergeCell ref="C18:U18"/>
     <mergeCell ref="C45:U45"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="R3:S3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
